--- a/2026/GALERIA/Agosto/GALERIA Agosto.xlsx
+++ b/2026/GALERIA/Agosto/GALERIA Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GALERIA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FF6DEB-E080-4823-AAA4-233A1527B1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B2D203-C2C5-457E-9A06-EA6D0FDCEC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$100</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$101</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="114">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -337,27 +342,15 @@
     <t xml:space="preserve">PREVISION ORDINARIA </t>
   </si>
   <si>
-    <t>Debito 08/07</t>
-  </si>
-  <si>
-    <t>Debito 13/07</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fotocopias BYN </t>
   </si>
   <si>
-    <t>A LA ADMINISTRACION SE LE DEBE EN CONCEPTO DE HONORARIOS NO COBRADOS (EN LOS MESES MENCIONADOS) UN TOTAL DEL $1.981.282,36 - EN JULIO SE ABONAN $400.000 - LA DEUDA DESCIENDE A $1.581.282,36</t>
-  </si>
-  <si>
     <t xml:space="preserve">GASTOS BANCARIOS </t>
   </si>
   <si>
     <t xml:space="preserve">COMISION POR CUENTA </t>
   </si>
   <si>
-    <t>Gasto cotillon mundial - Autorizado en el impaz de la administracion</t>
-  </si>
-  <si>
     <t>Local 15: Deposito 270.000 el día 17/3/2026 - Esta como no identificado en Junio - Este mes debe abonar: $135.138,15</t>
   </si>
   <si>
@@ -367,13 +360,25 @@
     <t>CUIT DEL EDIFICIO: 30-66055743-8 - PERÍODO:  agosto - HORARIOS DE ATENCION: LUNES A VIERNES 10 A 15HS</t>
   </si>
   <si>
-    <t>Honorarios administracion - Se cobraran durante el mes de agosto</t>
-  </si>
-  <si>
     <t>Seguro de vida Sra. Silvana - La Holando - Mes de julio</t>
   </si>
   <si>
     <t>Gasto particular: Reliquidacion de deuda UF 9 y 26</t>
+  </si>
+  <si>
+    <t>Debito 12/08</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - leer cartel debajo</t>
+  </si>
+  <si>
+    <t>A LA ADMINISTRACION SE LE DEBE EN CONCEPTO DE HONORARIOS NO COBRADOS (EN LOS MESES MENCIONADOS) UN TOTAL DEL $1.981.282,36 - LA DEUDA DESCIENDE A $1.581.282,36</t>
+  </si>
+  <si>
+    <t>Deposito ya identificado 27/03</t>
+  </si>
+  <si>
+    <t>Punitorios mal cobrados</t>
   </si>
 </sst>
 </file>
@@ -388,7 +393,7 @@
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -568,6 +573,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -995,7 +1007,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="219">
+  <cellXfs count="218">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1234,11 +1246,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1293,6 +1302,45 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1311,12 +1359,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1332,43 +1374,10 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1447,9 +1456,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1487,9 +1496,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1522,9 +1531,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1557,9 +1583,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1733,21 +1776,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M104"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M105"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="15"/>
       <c r="B1" s="73" t="s">
         <v>84</v>
@@ -1756,7 +1799,7 @@
       <c r="D1" s="73"/>
       <c r="E1" s="74"/>
     </row>
-    <row r="2" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="75" t="s">
         <v>47</v>
@@ -1765,7 +1808,7 @@
       <c r="D2" s="75"/>
       <c r="E2" s="76"/>
     </row>
-    <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="93" t="s">
         <v>45</v>
@@ -1774,7 +1817,7 @@
       <c r="D3" s="93"/>
       <c r="E3" s="76"/>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
@@ -1785,16 +1828,16 @@
       <c r="D4" s="20"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="17"/>
       <c r="D5" s="75"/>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>82</v>
       </c>
@@ -1803,57 +1846,57 @@
       <c r="D6" s="20"/>
       <c r="E6" s="21"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="175" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="175"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="175"/>
-      <c r="C9" s="175"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="175"/>
-      <c r="C10" s="175"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="183" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="174" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="174"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="174"/>
+      <c r="C9" s="174"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="174"/>
+      <c r="C10" s="174"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="182" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="183"/>
-      <c r="C13" s="183"/>
-      <c r="D13" s="183"/>
-      <c r="E13" s="183"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="183"/>
-      <c r="B14" s="183"/>
-      <c r="C14" s="183"/>
-      <c r="D14" s="183"/>
-      <c r="E14" s="183"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="183"/>
-      <c r="B15" s="183"/>
-      <c r="C15" s="183"/>
-      <c r="D15" s="183"/>
-      <c r="E15" s="183"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="183"/>
-      <c r="B16" s="183"/>
-      <c r="C16" s="183"/>
-      <c r="D16" s="183"/>
-      <c r="E16" s="183"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="182"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="182"/>
+      <c r="E13" s="182"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="182"/>
+      <c r="B14" s="182"/>
+      <c r="C14" s="182"/>
+      <c r="D14" s="182"/>
+      <c r="E14" s="182"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="182"/>
+      <c r="B15" s="182"/>
+      <c r="C15" s="182"/>
+      <c r="D15" s="182"/>
+      <c r="E15" s="182"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="182"/>
+      <c r="B16" s="182"/>
+      <c r="C16" s="182"/>
+      <c r="D16" s="182"/>
+      <c r="E16" s="182"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>22</v>
       </c>
@@ -1862,7 +1905,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
         <v>36</v>
       </c>
@@ -1872,22 +1915,20 @@
       <c r="E21" s="98"/>
       <c r="G21" s="22"/>
     </row>
-    <row r="22" spans="1:8" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="176" t="s">
-        <v>111</v>
-      </c>
-      <c r="B22" s="177"/>
+    <row r="22" spans="1:8" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="175" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="176"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="217">
-        <v>400000</v>
-      </c>
-      <c r="E22" s="121" t="s">
-        <v>102</v>
-      </c>
+      <c r="D22" s="173">
+        <v>0</v>
+      </c>
+      <c r="E22" s="121"/>
       <c r="F22" s="48"/>
       <c r="H22" s="22"/>
     </row>
-    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="29" t="s">
         <v>33</v>
       </c>
@@ -1896,10 +1937,10 @@
       <c r="D23" s="135"/>
       <c r="E23" s="162">
         <f>D22</f>
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="36" t="s">
         <v>49</v>
       </c>
@@ -1908,31 +1949,31 @@
       <c r="D24" s="134"/>
       <c r="E24" s="106"/>
     </row>
-    <row r="25" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="176" t="s">
+    <row r="25" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="175" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="177"/>
+      <c r="B25" s="176"/>
       <c r="C25" s="133"/>
-      <c r="D25" s="218">
+      <c r="D25" s="216">
         <v>149073.01</v>
       </c>
       <c r="E25" s="121" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="176" t="s">
-        <v>112</v>
-      </c>
-      <c r="B26" s="177"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="175" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" s="176"/>
       <c r="C26" s="133"/>
       <c r="D26" s="168">
         <v>0</v>
       </c>
       <c r="E26" s="121"/>
     </row>
-    <row r="27" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="29" t="s">
         <v>1</v>
       </c>
@@ -1945,7 +1986,7 @@
       </c>
       <c r="G27" s="151"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="38" t="s">
         <v>35</v>
       </c>
@@ -1954,7 +1995,7 @@
       <c r="D28" s="43"/>
       <c r="E28" s="100"/>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>78</v>
       </c>
@@ -1963,20 +2004,18 @@
       <c r="D29" s="120"/>
       <c r="E29" s="104"/>
     </row>
-    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="169">
-        <v>717234.68</v>
-      </c>
-      <c r="E30" s="121" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E30" s="121"/>
+    </row>
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>77</v>
       </c>
@@ -1985,7 +2024,7 @@
       <c r="D31" s="120"/>
       <c r="E31" s="104"/>
     </row>
-    <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>77</v>
       </c>
@@ -1994,14 +2033,14 @@
       <c r="D32" s="120"/>
       <c r="E32" s="104"/>
     </row>
-    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="120"/>
       <c r="E33" s="104"/>
     </row>
-    <row r="34" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="29" t="s">
         <v>2</v>
       </c>
@@ -2010,10 +2049,10 @@
       <c r="D34" s="42"/>
       <c r="E34" s="99">
         <f>SUM(D29:D33)</f>
-        <v>717234.68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="38" t="s">
         <v>34</v>
       </c>
@@ -2022,531 +2061,535 @@
       <c r="D35" s="42"/>
       <c r="E35" s="102"/>
     </row>
-    <row r="36" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="171" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
       <c r="D36" s="41">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="E36" s="121"/>
       <c r="J36" s="60"/>
     </row>
-    <row r="37" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="171" t="s">
-        <v>107</v>
-      </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="41">
-        <v>64000</v>
-      </c>
-      <c r="E37" s="172"/>
-      <c r="J37" s="130"/>
-    </row>
-    <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="29" t="s">
+    <row r="37" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B38" s="38"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="106">
-        <f>SUM(D36:D37)</f>
-        <v>69000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="38" t="s">
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="106">
+        <f>SUM(D36:D36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="71"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="102"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B38" s="71"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="102"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="120">
+        <v>0</v>
+      </c>
+      <c r="E39" s="107"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
-      <c r="D40" s="120">
-        <v>0</v>
-      </c>
-      <c r="E40" s="107"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="120">
-        <v>31684.27</v>
-      </c>
-      <c r="E41" s="105"/>
-    </row>
-    <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="59" t="s">
+      <c r="D40" s="120"/>
+      <c r="E40" s="105"/>
+    </row>
+    <row r="41" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="B42" s="59"/>
-      <c r="C42" s="59"/>
-      <c r="D42" s="108"/>
-      <c r="E42" s="99">
-        <f>SUM(D40:D41)</f>
-        <v>31684.27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="97"/>
-      <c r="E43" s="109"/>
-    </row>
-    <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="32" t="s">
+      <c r="B41" s="59"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="108"/>
+      <c r="E41" s="99">
+        <f>SUM(D39:D40)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="97"/>
+      <c r="E42" s="109"/>
+    </row>
+    <row r="43" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="110"/>
-      <c r="E44" s="111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="1"/>
-      <c r="D45" s="112"/>
-      <c r="E45" s="113"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="110"/>
+      <c r="E43" s="111">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+      <c r="D44" s="112"/>
+      <c r="E44" s="113"/>
+      <c r="F44" s="51"/>
+    </row>
+    <row r="45" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B45" s="10"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="114"/>
+      <c r="E45" s="115">
+        <f>(SUM(E21:E43))</f>
+        <v>1649073.01</v>
+      </c>
       <c r="F45" s="51"/>
     </row>
-    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="10"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="114"/>
-      <c r="E46" s="115">
-        <f>(SUM(E21:E44))</f>
-        <v>1366991.96</v>
-      </c>
-      <c r="F46" s="51"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D46" s="112"/>
+      <c r="E46" s="112"/>
+    </row>
+    <row r="47" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D47" s="112"/>
       <c r="E47" s="112"/>
     </row>
-    <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D48" s="112"/>
-      <c r="E48" s="112"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="11" t="s">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="12"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="116"/>
-      <c r="E49" s="117"/>
-    </row>
-    <row r="50" spans="1:5" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="176"/>
-      <c r="B50" s="177"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="116"/>
+      <c r="E48" s="117"/>
+    </row>
+    <row r="49" spans="1:5" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="175"/>
+      <c r="B49" s="176"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="103"/>
+      <c r="E49" s="101"/>
+    </row>
+    <row r="50" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="175"/>
+      <c r="B50" s="176"/>
       <c r="C50" s="5"/>
       <c r="D50" s="103"/>
       <c r="E50" s="101"/>
     </row>
-    <row r="51" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="176"/>
-      <c r="B51" s="177"/>
+    <row r="51" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="180"/>
+      <c r="B51" s="181"/>
       <c r="C51" s="5"/>
       <c r="D51" s="103"/>
       <c r="E51" s="101"/>
     </row>
-    <row r="52" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="181"/>
-      <c r="B52" s="182"/>
-      <c r="C52" s="5"/>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="122"/>
+      <c r="B52" s="123"/>
+      <c r="C52" s="60"/>
       <c r="D52" s="103"/>
       <c r="E52" s="101"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="122"/>
-      <c r="B53" s="123"/>
-      <c r="C53" s="60"/>
-      <c r="D53" s="103"/>
-      <c r="E53" s="101"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="57"/>
-      <c r="B54" s="56"/>
-      <c r="C54" s="56"/>
-      <c r="D54" s="63"/>
-      <c r="E54" s="63">
-        <f>SUM(D50:D53)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="32" t="s">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="57"/>
+      <c r="B53" s="56"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="63"/>
+      <c r="E53" s="63">
+        <f>SUM(D49:D52)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="32"/>
-      <c r="C57" s="32"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="125"/>
-    </row>
-    <row r="58" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="59" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="3" t="s">
+      <c r="B56" s="32"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="125"/>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B59" s="10"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="72">
-        <f>E54+E57</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="61" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B58" s="10"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="72">
+        <f>E53+E56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="B60" s="95">
+        <f>E45</f>
+        <v>1649073.01</v>
+      </c>
+      <c r="D60" s="51"/>
+    </row>
+    <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B61" s="95">
-        <f>E46</f>
-        <v>1366991.96</v>
-      </c>
-      <c r="D61" s="51"/>
-    </row>
-    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f>E45-E43</f>
+        <v>149073.01</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="94" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B62" s="95">
-        <f>E46-E44</f>
-        <v>1366991.96</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f>E58-E56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="94" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B63" s="95">
-        <f>E59-E57</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="94" t="s">
-        <v>55</v>
-      </c>
-      <c r="B64" s="95">
-        <f>E59</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="180" t="s">
+        <f>E58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="179" t="s">
         <v>93</v>
       </c>
-      <c r="B67" s="180"/>
-      <c r="C67" s="180"/>
-      <c r="D67" s="180"/>
-      <c r="E67" s="180"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="180"/>
-      <c r="B68" s="180"/>
-      <c r="C68" s="180"/>
-      <c r="D68" s="180"/>
-      <c r="E68" s="180"/>
-    </row>
-    <row r="69" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="180"/>
-      <c r="B69" s="180"/>
-      <c r="C69" s="180"/>
-      <c r="D69" s="180"/>
-      <c r="E69" s="180"/>
-    </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="184" t="s">
-        <v>104</v>
-      </c>
-      <c r="B71" s="185"/>
-      <c r="C71" s="185"/>
-      <c r="D71" s="185"/>
-      <c r="E71" s="186"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="187"/>
-      <c r="B72" s="188"/>
-      <c r="C72" s="188"/>
-      <c r="D72" s="188"/>
-      <c r="E72" s="189"/>
-    </row>
-    <row r="73" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="190"/>
-      <c r="B73" s="191"/>
-      <c r="C73" s="191"/>
-      <c r="D73" s="191"/>
-      <c r="E73" s="192"/>
-    </row>
-    <row r="74" spans="1:5" s="130" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="163"/>
-      <c r="B74" s="163"/>
-      <c r="C74" s="163"/>
-      <c r="D74" s="163"/>
-      <c r="E74" s="163"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="165" t="s">
+      <c r="B66" s="179"/>
+      <c r="C66" s="179"/>
+      <c r="D66" s="179"/>
+      <c r="E66" s="179"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="179"/>
+      <c r="B67" s="179"/>
+      <c r="C67" s="179"/>
+      <c r="D67" s="179"/>
+      <c r="E67" s="179"/>
+    </row>
+    <row r="68" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="179"/>
+      <c r="B68" s="179"/>
+      <c r="C68" s="179"/>
+      <c r="D68" s="179"/>
+      <c r="E68" s="179"/>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="183" t="s">
+        <v>111</v>
+      </c>
+      <c r="B70" s="184"/>
+      <c r="C70" s="184"/>
+      <c r="D70" s="184"/>
+      <c r="E70" s="185"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="186"/>
+      <c r="B71" s="187"/>
+      <c r="C71" s="187"/>
+      <c r="D71" s="187"/>
+      <c r="E71" s="188"/>
+    </row>
+    <row r="72" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="189"/>
+      <c r="B72" s="190"/>
+      <c r="C72" s="190"/>
+      <c r="D72" s="190"/>
+      <c r="E72" s="191"/>
+    </row>
+    <row r="73" spans="1:5" s="130" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="163"/>
+      <c r="B73" s="163"/>
+      <c r="C73" s="163"/>
+      <c r="D73" s="163"/>
+      <c r="E73" s="163"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="165" t="s">
         <v>51</v>
       </c>
-      <c r="B75" s="166"/>
-      <c r="C75" s="23"/>
-    </row>
-    <row r="76" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="167" t="s">
+      <c r="B74" s="166"/>
+      <c r="C74" s="23"/>
+    </row>
+    <row r="75" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="167" t="s">
         <v>90</v>
       </c>
-      <c r="B76" s="124">
-        <v>2760985.03</v>
-      </c>
-      <c r="C76" s="25"/>
-    </row>
-    <row r="77" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="124">
+        <v>1232001.3899999999</v>
+      </c>
+      <c r="C75" s="25"/>
+    </row>
+    <row r="76" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B76" s="47">
+        <f>PRORRATEO!G35</f>
+        <v>926091.54999999993</v>
+      </c>
+      <c r="C76" s="23"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="B77" s="47">
-        <f>PRORRATEO!G35</f>
-        <v>329891.28999999998</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B77" s="47"/>
       <c r="C77" s="23"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="B78" s="47"/>
+    <row r="78" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="B78" s="170">
+        <v>-99000</v>
+      </c>
       <c r="C78" s="23"/>
     </row>
-    <row r="79" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="B79" s="170">
+        <v>-270000</v>
+      </c>
+      <c r="C79" s="23"/>
+    </row>
+    <row r="80" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="B79" s="170">
-        <v>-99000</v>
-      </c>
-      <c r="C79" s="23"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="24" t="s">
+      <c r="B80" s="170">
+        <v>-86980</v>
+      </c>
+      <c r="C80" s="23"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B80" s="47">
-        <f>B99</f>
-        <v>0</v>
-      </c>
-      <c r="C80" s="23"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="24" t="s">
+      <c r="B81" s="47">
+        <f>B100</f>
+        <v>0</v>
+      </c>
+      <c r="C81" s="23"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B81" s="47">
-        <v>0</v>
-      </c>
-      <c r="C81" s="23"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="46" t="s">
+      <c r="B82" s="47">
+        <v>0</v>
+      </c>
+      <c r="C82" s="23"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="B82" s="170">
-        <f>-B62</f>
-        <v>-1366991.96</v>
-      </c>
-      <c r="C82" s="23"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="27" t="s">
+      <c r="B83" s="170">
+        <f>-B61</f>
+        <v>-149073.01</v>
+      </c>
+      <c r="C83" s="23"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B83" s="105">
-        <f>-(B63)</f>
-        <v>0</v>
-      </c>
-      <c r="C83" s="23"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="34" t="s">
+      <c r="B84" s="105">
+        <f>-(B62)</f>
+        <v>0</v>
+      </c>
+      <c r="C84" s="23"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="B84" s="124">
-        <f>SUM(B76:B83)</f>
-        <v>1624884.3599999999</v>
-      </c>
-      <c r="C84" s="26"/>
-      <c r="D84" s="151"/>
-      <c r="E84" s="151"/>
-      <c r="F84" s="151"/>
-    </row>
-    <row r="85" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B85" s="48"/>
+      <c r="B85" s="124">
+        <f>SUM(B75:B84)</f>
+        <v>1553039.93</v>
+      </c>
       <c r="C85" s="26"/>
-      <c r="D85" s="51"/>
-    </row>
-    <row r="86" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="49"/>
+      <c r="D85" s="151"/>
+      <c r="E85" s="151"/>
+      <c r="F85" s="151"/>
+    </row>
+    <row r="86" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="48"/>
       <c r="C86" s="26"/>
-    </row>
-    <row r="87" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87"/>
-      <c r="B87" s="48"/>
-      <c r="C87" s="44"/>
-    </row>
-    <row r="88" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="35" t="s">
+      <c r="D86" s="51"/>
+    </row>
+    <row r="87" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="49"/>
+      <c r="C87" s="26"/>
+    </row>
+    <row r="88" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="44"/>
+    </row>
+    <row r="89" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B88" s="40"/>
-      <c r="C88" s="44"/>
-      <c r="D88" s="54"/>
-    </row>
-    <row r="89" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="5" t="s">
+      <c r="B89" s="40"/>
+      <c r="C89" s="44"/>
+      <c r="D89" s="54"/>
+    </row>
+    <row r="90" spans="1:6" s="45" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B89" s="41">
-        <v>0</v>
-      </c>
-      <c r="C89" s="44"/>
-    </row>
-    <row r="90" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="5" t="s">
+      <c r="B90" s="41">
+        <v>0</v>
+      </c>
+      <c r="C90" s="44"/>
+    </row>
+    <row r="91" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B90" s="40">
-        <v>0</v>
-      </c>
-      <c r="C90" s="26"/>
-      <c r="D90" s="51"/>
-    </row>
-    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="5" t="s">
+      <c r="B91" s="40">
+        <v>0</v>
+      </c>
+      <c r="C91" s="26"/>
+      <c r="D91" s="51"/>
+    </row>
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B91" s="40">
-        <v>0</v>
-      </c>
-      <c r="C91" s="26"/>
-    </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="5" t="s">
+      <c r="B92" s="40">
+        <v>0</v>
+      </c>
+      <c r="C92" s="26"/>
+    </row>
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B92" s="40">
-        <v>0</v>
-      </c>
-      <c r="C92" s="28"/>
-    </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="35" t="s">
+      <c r="B93" s="40">
+        <v>0</v>
+      </c>
+      <c r="C93" s="28"/>
+    </row>
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="B93" s="55">
-        <f>SUM(B89:B92)</f>
-        <v>0</v>
-      </c>
-      <c r="C93" s="23"/>
-    </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="95" spans="1:6" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="179" t="s">
+      <c r="B94" s="55">
+        <f>SUM(B90:B93)</f>
+        <v>0</v>
+      </c>
+      <c r="C94" s="23"/>
+    </row>
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:6" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="B96" s="179"/>
-      <c r="C96" s="179"/>
-    </row>
-    <row r="97" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="179"/>
-      <c r="B97" s="179"/>
-      <c r="C97" s="179"/>
-    </row>
-    <row r="98" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="118"/>
-      <c r="B98" s="40"/>
-      <c r="C98" s="164">
+      <c r="B97" s="178"/>
+      <c r="C97" s="178"/>
+    </row>
+    <row r="98" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="178"/>
+      <c r="B98" s="178"/>
+      <c r="C98" s="178"/>
+    </row>
+    <row r="99" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="118"/>
+      <c r="B99" s="40"/>
+      <c r="C99" s="164">
         <v>40000</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A99" s="52" t="s">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="B99" s="119">
-        <f>SUM(B98:B98)</f>
-        <v>0</v>
-      </c>
-      <c r="C99" s="53"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M100" s="8"/>
-    </row>
-    <row r="101" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="178"/>
-      <c r="B101" s="178"/>
-      <c r="C101" s="178"/>
-      <c r="D101" s="178"/>
-      <c r="E101" s="178"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A102" s="178"/>
-      <c r="B102" s="178"/>
-      <c r="C102" s="178"/>
-      <c r="D102" s="178"/>
-      <c r="E102" s="178"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A103" s="178"/>
-      <c r="B103" s="178"/>
-      <c r="C103" s="178"/>
-      <c r="D103" s="178"/>
-      <c r="E103" s="178"/>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A104" s="178"/>
-      <c r="B104" s="178"/>
-      <c r="C104" s="178"/>
-      <c r="D104" s="178"/>
-      <c r="E104" s="178"/>
+      <c r="B100" s="119">
+        <f>SUM(B99:B99)</f>
+        <v>0</v>
+      </c>
+      <c r="C100" s="53"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M101" s="8"/>
+    </row>
+    <row r="102" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="177"/>
+      <c r="B102" s="177"/>
+      <c r="C102" s="177"/>
+      <c r="D102" s="177"/>
+      <c r="E102" s="177"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" s="177"/>
+      <c r="B103" s="177"/>
+      <c r="C103" s="177"/>
+      <c r="D103" s="177"/>
+      <c r="E103" s="177"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" s="177"/>
+      <c r="B104" s="177"/>
+      <c r="C104" s="177"/>
+      <c r="D104" s="177"/>
+      <c r="E104" s="177"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" s="177"/>
+      <c r="B105" s="177"/>
+      <c r="C105" s="177"/>
+      <c r="D105" s="177"/>
+      <c r="E105" s="177"/>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A101:E104"/>
-    <mergeCell ref="A96:C97"/>
-    <mergeCell ref="A67:E69"/>
+    <mergeCell ref="A102:E105"/>
+    <mergeCell ref="A97:C98"/>
+    <mergeCell ref="A66:E68"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A49:B49"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A71:E73"/>
+    <mergeCell ref="A70:E72"/>
     <mergeCell ref="A26:B26"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2558,36 +2601,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="4.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" customWidth="1"/>
-    <col min="8" max="9" width="10.5546875" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
-    <col min="14" max="14" width="0.44140625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.109375" customWidth="1"/>
-    <col min="16" max="16" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+    <col min="8" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="14" max="14" width="0.42578125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" customWidth="1"/>
+    <col min="16" max="16" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
-      <c r="C1" s="193" t="s">
+      <c r="C1" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="194"/>
-      <c r="E1" s="194"/>
-      <c r="F1" s="194"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -2599,13 +2642,13 @@
       <c r="O1" s="62"/>
       <c r="P1" s="22"/>
     </row>
-    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="194"/>
-      <c r="D2" s="194"/>
-      <c r="E2" s="194"/>
-      <c r="F2" s="194"/>
+      <c r="C2" s="206"/>
+      <c r="D2" s="206"/>
+      <c r="E2" s="206"/>
+      <c r="F2" s="206"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -2617,13 +2660,13 @@
       <c r="O2" s="62"/>
       <c r="P2" s="22"/>
     </row>
-    <row r="3" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
-      <c r="C3" s="194"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="194"/>
-      <c r="F3" s="194"/>
+      <c r="C3" s="206"/>
+      <c r="D3" s="206"/>
+      <c r="E3" s="206"/>
+      <c r="F3" s="206"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -2631,11 +2674,11 @@
         <v>80</v>
       </c>
       <c r="K3" s="6"/>
-      <c r="L3" s="195">
+      <c r="L3" s="207">
         <f>Q3</f>
         <v>1668874.9300000002</v>
       </c>
-      <c r="M3" s="195"/>
+      <c r="M3" s="207"/>
       <c r="N3" s="62"/>
       <c r="O3" s="62"/>
       <c r="P3" s="22"/>
@@ -2643,13 +2686,13 @@
         <v>1668874.9300000002</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="194"/>
-      <c r="D4" s="194"/>
-      <c r="E4" s="194"/>
-      <c r="F4" s="194"/>
+      <c r="C4" s="206"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="206"/>
+      <c r="F4" s="206"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -2657,99 +2700,99 @@
         <v>99</v>
       </c>
       <c r="K4" s="6"/>
-      <c r="L4" s="196"/>
-      <c r="M4" s="196"/>
+      <c r="L4" s="208"/>
+      <c r="M4" s="208"/>
       <c r="N4" s="64"/>
       <c r="O4" s="64"/>
     </row>
-    <row r="5" spans="1:18" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="201" t="s">
+    <row r="5" spans="1:18" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="211" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="202"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="202"/>
-      <c r="E5" s="202"/>
-      <c r="F5" s="202"/>
-      <c r="G5" s="202"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="202"/>
-      <c r="K5" s="202"/>
-      <c r="L5" s="202"/>
-      <c r="M5" s="202"/>
-      <c r="N5" s="202"/>
-      <c r="O5" s="203"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="197" t="s">
+      <c r="B5" s="212"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="212"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="212"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="212"/>
+      <c r="K5" s="212"/>
+      <c r="L5" s="212"/>
+      <c r="M5" s="212"/>
+      <c r="N5" s="212"/>
+      <c r="O5" s="213"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="209" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="199" t="s">
+      <c r="B6" s="193" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="199" t="s">
+      <c r="C6" s="193" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="199" t="s">
+      <c r="D6" s="193" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="199" t="s">
+      <c r="E6" s="193" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="199" t="s">
+      <c r="F6" s="193" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="199" t="s">
+      <c r="G6" s="193" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="215" t="s">
+      <c r="H6" s="202" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="215" t="s">
+      <c r="I6" s="202" t="s">
         <v>87</v>
       </c>
-      <c r="J6" s="210" t="s">
+      <c r="J6" s="197" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="210" t="s">
+      <c r="K6" s="197" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="213" t="s">
+      <c r="L6" s="200" t="s">
         <v>54</v>
       </c>
       <c r="M6" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="208" t="s">
+      <c r="N6" s="195" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="204" t="s">
+      <c r="O6" s="214" t="s">
         <v>52</v>
       </c>
       <c r="R6" s="51"/>
     </row>
-    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="198"/>
-      <c r="B7" s="200"/>
-      <c r="C7" s="200"/>
-      <c r="D7" s="207"/>
-      <c r="E7" s="200"/>
-      <c r="F7" s="200"/>
-      <c r="G7" s="200"/>
-      <c r="H7" s="216"/>
-      <c r="I7" s="216"/>
-      <c r="J7" s="211"/>
-      <c r="K7" s="212"/>
-      <c r="L7" s="214"/>
+    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="210"/>
+      <c r="B7" s="204"/>
+      <c r="C7" s="204"/>
+      <c r="D7" s="194"/>
+      <c r="E7" s="204"/>
+      <c r="F7" s="204"/>
+      <c r="G7" s="204"/>
+      <c r="H7" s="203"/>
+      <c r="I7" s="203"/>
+      <c r="J7" s="198"/>
+      <c r="K7" s="199"/>
+      <c r="L7" s="201"/>
       <c r="M7" s="65" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="N7" s="209"/>
-      <c r="O7" s="205"/>
-    </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N7" s="196"/>
+      <c r="O7" s="215"/>
+    </row>
+    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -2764,18 +2807,18 @@
         <v>6.8</v>
       </c>
       <c r="F8" s="78">
-        <v>342539.01</v>
+        <v>507403.01</v>
       </c>
       <c r="G8" s="79">
         <v>0</v>
       </c>
       <c r="H8" s="80">
         <f>F8-G8</f>
-        <v>342539.01</v>
+        <v>507403.01</v>
       </c>
       <c r="I8" s="80">
         <f>IF(H8&gt;0,H8*15%,0)</f>
-        <v>51380.851499999997</v>
+        <v>76110.451499999996</v>
       </c>
       <c r="J8" s="127">
         <f t="shared" ref="J8:J33" si="0">L$4*E8/100</f>
@@ -2790,21 +2833,21 @@
       </c>
       <c r="M8" s="83">
         <f t="shared" ref="M8:M33" si="2">ROUND(SUM(H8:L8),0) + P8</f>
-        <v>507403.01</v>
+        <v>696997.01</v>
       </c>
       <c r="N8" s="84">
         <f>ROUND(M8*6% + M8,0) + P8</f>
-        <v>537847.01</v>
+        <v>738817.01</v>
       </c>
       <c r="O8" s="85">
         <f>ROUND(M8*3%,0) + M8</f>
-        <v>522625.01</v>
+        <v>717907.01</v>
       </c>
       <c r="P8" s="51">
         <v>0.01</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="60" t="s">
         <v>9</v>
       </c>
@@ -2820,14 +2863,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="F9" s="79">
-        <v>-367446.98</v>
+        <v>-282333.98</v>
       </c>
       <c r="G9" s="79">
         <v>0</v>
       </c>
       <c r="H9" s="96">
         <f>F9-G9</f>
-        <v>-367446.98</v>
+        <v>-282333.98</v>
       </c>
       <c r="I9" s="96">
         <f>IF(H9&gt;0,H9*15%,0)</f>
@@ -2846,15 +2889,15 @@
       </c>
       <c r="M9" s="148">
         <f t="shared" si="2"/>
-        <v>-282333.98</v>
+        <v>-197220.98</v>
       </c>
       <c r="N9" s="149">
         <f t="shared" ref="N9:N33" si="3">ROUND(M9*6% + M9,0) + P9</f>
-        <v>-299273.98</v>
+        <v>-209053.98</v>
       </c>
       <c r="O9" s="150">
         <f t="shared" ref="O9:O33" si="4">ROUND(M9*3%,0) + M9</f>
-        <v>-290803.98</v>
+        <v>-203137.98</v>
       </c>
       <c r="P9" s="51">
         <f>P8+0.01</f>
@@ -2865,7 +2908,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="60" t="s">
         <v>9</v>
       </c>
@@ -2881,10 +2924,11 @@
         <v>5.6</v>
       </c>
       <c r="F10" s="79">
-        <v>159502.03</v>
-      </c>
-      <c r="G10" s="79">
-        <v>159502.03</v>
+        <v>93457.03</v>
+      </c>
+      <c r="G10" s="217">
+        <f>F10</f>
+        <v>93457.03</v>
       </c>
       <c r="H10" s="96">
         <f>F10-G10</f>
@@ -2922,7 +2966,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
@@ -2938,14 +2982,14 @@
         <v>2.8</v>
       </c>
       <c r="F11" s="78">
-        <v>-1165520.96</v>
+        <v>-1118791.96</v>
       </c>
       <c r="G11" s="79">
         <v>0</v>
       </c>
       <c r="H11" s="80">
         <f t="shared" ref="H11:H16" si="7">F11-G11</f>
-        <v>-1165520.96</v>
+        <v>-1118791.96</v>
       </c>
       <c r="I11" s="80">
         <f t="shared" ref="I11:I33" si="8">IF(H11&gt;0,H11*15%,0)</f>
@@ -2964,15 +3008,15 @@
       </c>
       <c r="M11" s="83">
         <f t="shared" si="2"/>
-        <v>-1118791.96</v>
+        <v>-1072062.96</v>
       </c>
       <c r="N11" s="84">
         <f t="shared" si="3"/>
-        <v>-1185918.96</v>
+        <v>-1136386.96</v>
       </c>
       <c r="O11" s="85">
         <f t="shared" si="4"/>
-        <v>-1152355.96</v>
+        <v>-1104224.96</v>
       </c>
       <c r="P11" s="51">
         <f t="shared" si="6"/>
@@ -2982,7 +3026,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
@@ -2998,18 +3042,19 @@
         <v>2.8</v>
       </c>
       <c r="F12" s="78">
-        <v>75849.05</v>
-      </c>
-      <c r="G12" s="79">
-        <v>0</v>
+        <v>133955.04999999999</v>
+      </c>
+      <c r="G12" s="217">
+        <f>137974.05</f>
+        <v>137974.04999999999</v>
       </c>
       <c r="H12" s="80">
         <f t="shared" si="7"/>
-        <v>75849.05</v>
+        <v>-4019</v>
       </c>
       <c r="I12" s="80">
         <f t="shared" si="8"/>
-        <v>11377.3575</v>
+        <v>0</v>
       </c>
       <c r="J12" s="127">
         <f t="shared" si="0"/>
@@ -3024,15 +3069,15 @@
       </c>
       <c r="M12" s="83">
         <f t="shared" si="2"/>
-        <v>133955.04999999999</v>
+        <v>42709.05</v>
       </c>
       <c r="N12" s="84">
         <f t="shared" si="3"/>
-        <v>141992.04999999999</v>
+        <v>45272.05</v>
       </c>
       <c r="O12" s="85">
         <f t="shared" si="4"/>
-        <v>137974.04999999999</v>
+        <v>43990.05</v>
       </c>
       <c r="P12" s="51">
         <f t="shared" si="6"/>
@@ -3040,7 +3085,7 @@
       </c>
       <c r="R12" s="51"/>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>11</v>
       </c>
@@ -3056,14 +3101,14 @@
         <v>2.8</v>
       </c>
       <c r="F13" s="78">
-        <v>-74212.94</v>
+        <v>-27483.94</v>
       </c>
       <c r="G13" s="79">
         <v>0</v>
       </c>
       <c r="H13" s="80">
         <f t="shared" si="7"/>
-        <v>-74212.94</v>
+        <v>-27483.94</v>
       </c>
       <c r="I13" s="80">
         <f t="shared" si="8"/>
@@ -3082,15 +3127,15 @@
       </c>
       <c r="M13" s="83">
         <f t="shared" si="2"/>
-        <v>-27483.94</v>
+        <v>19245.060000000001</v>
       </c>
       <c r="N13" s="84">
         <f t="shared" si="3"/>
-        <v>-29132.94</v>
+        <v>20400.060000000001</v>
       </c>
       <c r="O13" s="85">
         <f t="shared" si="4"/>
-        <v>-28308.94</v>
+        <v>19822.060000000001</v>
       </c>
       <c r="P13" s="51">
         <f t="shared" si="6"/>
@@ -3100,7 +3145,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>11</v>
       </c>
@@ -3116,18 +3161,18 @@
         <v>4</v>
       </c>
       <c r="F14" s="154">
-        <v>2537643.0699999998</v>
+        <v>2985045.07</v>
       </c>
       <c r="G14" s="154">
         <v>0</v>
       </c>
       <c r="H14" s="155">
         <f t="shared" si="7"/>
-        <v>2537643.0699999998</v>
+        <v>2985045.07</v>
       </c>
       <c r="I14" s="155">
         <f t="shared" si="8"/>
-        <v>380646.46049999999</v>
+        <v>447756.76049999997</v>
       </c>
       <c r="J14" s="156">
         <f t="shared" si="0"/>
@@ -3142,22 +3187,22 @@
       </c>
       <c r="M14" s="158">
         <f t="shared" si="2"/>
-        <v>2985045.07</v>
+        <v>3499557.07</v>
       </c>
       <c r="N14" s="159">
         <f t="shared" si="3"/>
-        <v>3164148.07</v>
+        <v>3709530.07</v>
       </c>
       <c r="O14" s="160">
         <f t="shared" si="4"/>
-        <v>3074596.07</v>
+        <v>3604544.07</v>
       </c>
       <c r="P14" s="51">
         <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>12</v>
       </c>
@@ -3173,19 +3218,18 @@
         <v>3.2</v>
       </c>
       <c r="F15" s="138">
-        <v>29344.080000000002</v>
+        <v>53404.08</v>
       </c>
       <c r="G15" s="138">
-        <f>F15</f>
-        <v>29344.080000000002</v>
+        <v>0</v>
       </c>
       <c r="H15" s="139">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>53404.08</v>
       </c>
       <c r="I15" s="139">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8010.6120000000001</v>
       </c>
       <c r="J15" s="140">
         <f t="shared" si="0"/>
@@ -3200,22 +3244,22 @@
       </c>
       <c r="M15" s="142">
         <f t="shared" si="2"/>
-        <v>53404.08</v>
+        <v>114819.08</v>
       </c>
       <c r="N15" s="143">
         <f t="shared" si="3"/>
-        <v>56608.08</v>
+        <v>121708.08</v>
       </c>
       <c r="O15" s="144">
         <f t="shared" si="4"/>
-        <v>55006.080000000002</v>
+        <v>118264.08</v>
       </c>
       <c r="P15" s="51">
         <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>12</v>
       </c>
@@ -3231,18 +3275,18 @@
         <v>2.8</v>
       </c>
       <c r="F16" s="154">
-        <v>2220940.09</v>
+        <v>2600810.09</v>
       </c>
       <c r="G16" s="154">
         <v>0</v>
       </c>
       <c r="H16" s="155">
         <f t="shared" si="7"/>
-        <v>2220940.09</v>
+        <v>2600810.09</v>
       </c>
       <c r="I16" s="155">
         <f t="shared" si="8"/>
-        <v>333141.01349999994</v>
+        <v>390121.51349999994</v>
       </c>
       <c r="J16" s="156">
         <f t="shared" si="0"/>
@@ -3257,22 +3301,22 @@
       </c>
       <c r="M16" s="158">
         <f t="shared" si="2"/>
-        <v>2600810.09</v>
+        <v>3037660.09</v>
       </c>
       <c r="N16" s="159">
         <f t="shared" si="3"/>
-        <v>2756859.09</v>
+        <v>3219920.09</v>
       </c>
       <c r="O16" s="160">
         <f t="shared" si="4"/>
-        <v>2678834.09</v>
+        <v>3128790.09</v>
       </c>
       <c r="P16" s="51">
         <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>13</v>
       </c>
@@ -3288,7 +3332,7 @@
         <v>2.8</v>
       </c>
       <c r="F17" s="79">
-        <v>77428.100000000006</v>
+        <v>46728.1</v>
       </c>
       <c r="G17" s="79" t="s">
         <v>76</v>
@@ -3325,7 +3369,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
@@ -3341,7 +3385,7 @@
         <v>2.8</v>
       </c>
       <c r="F18" s="79">
-        <v>77428.11</v>
+        <v>46728.11</v>
       </c>
       <c r="G18" s="79" t="s">
         <v>76</v>
@@ -3378,7 +3422,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="60" t="s">
         <v>14</v>
       </c>
@@ -3394,18 +3438,19 @@
         <v>2.8</v>
       </c>
       <c r="F19" s="79">
-        <v>77428.12</v>
-      </c>
-      <c r="G19" s="79">
-        <v>0</v>
+        <v>135771.12</v>
+      </c>
+      <c r="G19" s="217">
+        <f>F19</f>
+        <v>135771.12</v>
       </c>
       <c r="H19" s="96">
         <f t="shared" ref="H19:H31" si="9">F19-G19</f>
-        <v>77428.12</v>
+        <v>0</v>
       </c>
       <c r="I19" s="96">
         <f t="shared" si="8"/>
-        <v>11614.217999999999</v>
+        <v>0</v>
       </c>
       <c r="J19" s="146">
         <f t="shared" si="0"/>
@@ -3420,22 +3465,22 @@
       </c>
       <c r="M19" s="148">
         <f t="shared" si="2"/>
-        <v>135771.12</v>
+        <v>46728.12</v>
       </c>
       <c r="N19" s="149">
         <f t="shared" si="3"/>
-        <v>143917.12</v>
+        <v>49532.12</v>
       </c>
       <c r="O19" s="150">
         <f t="shared" si="4"/>
-        <v>139844.12</v>
+        <v>48130.12</v>
       </c>
       <c r="P19" s="51">
         <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="60" t="s">
         <v>14</v>
       </c>
@@ -3451,18 +3496,18 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="F20" s="79">
-        <v>1375471.13</v>
+        <v>1666904.13</v>
       </c>
       <c r="G20" s="79">
         <v>0</v>
       </c>
       <c r="H20" s="96">
         <f t="shared" si="9"/>
-        <v>1375471.13</v>
+        <v>1666904.13</v>
       </c>
       <c r="I20" s="96">
         <f t="shared" si="8"/>
-        <v>206320.66949999999</v>
+        <v>250035.61949999997</v>
       </c>
       <c r="J20" s="146">
         <f t="shared" si="0"/>
@@ -3477,15 +3522,15 @@
       </c>
       <c r="M20" s="148">
         <f t="shared" si="2"/>
-        <v>1666904.13</v>
+        <v>2002052.13</v>
       </c>
       <c r="N20" s="149">
         <f t="shared" si="3"/>
-        <v>1766918.13</v>
+        <v>2122175.13</v>
       </c>
       <c r="O20" s="150">
         <f t="shared" si="4"/>
-        <v>1716911.13</v>
+        <v>2062114.13</v>
       </c>
       <c r="P20" s="51">
         <f t="shared" si="6"/>
@@ -3495,7 +3540,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>15</v>
       </c>
@@ -3511,18 +3556,18 @@
         <v>2.6</v>
       </c>
       <c r="F21" s="154">
-        <v>1494625.14</v>
+        <v>1762210.14</v>
       </c>
       <c r="G21" s="154">
         <v>0</v>
       </c>
       <c r="H21" s="155">
         <f t="shared" si="9"/>
-        <v>1494625.14</v>
+        <v>1762210.14</v>
       </c>
       <c r="I21" s="155">
         <f t="shared" si="8"/>
-        <v>224193.77099999998</v>
+        <v>264331.52099999995</v>
       </c>
       <c r="J21" s="156">
         <f t="shared" si="0"/>
@@ -3537,15 +3582,15 @@
       </c>
       <c r="M21" s="158">
         <f t="shared" si="2"/>
-        <v>1762210.14</v>
+        <v>2069932.14</v>
       </c>
       <c r="N21" s="159">
         <f t="shared" si="3"/>
-        <v>1867943.14</v>
+        <v>2194128.14</v>
       </c>
       <c r="O21" s="160">
         <f t="shared" si="4"/>
-        <v>1815076.14</v>
+        <v>2132030.1399999997</v>
       </c>
       <c r="P21" s="51">
         <f t="shared" si="6"/>
@@ -3555,15 +3600,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="174">
+      <c r="B22" s="68">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="C22" s="174" t="s">
+      <c r="C22" s="68" t="s">
         <v>71</v>
       </c>
       <c r="D22" s="86"/>
@@ -3571,18 +3616,19 @@
         <v>2.8</v>
       </c>
       <c r="F22" s="79">
-        <v>387295.15</v>
-      </c>
-      <c r="G22" s="79">
-        <v>0</v>
+        <v>492118.15</v>
+      </c>
+      <c r="G22" s="217">
+        <f>135138.15+270000+86980</f>
+        <v>492118.15</v>
       </c>
       <c r="H22" s="96">
         <f t="shared" si="9"/>
-        <v>387295.15</v>
+        <v>0</v>
       </c>
       <c r="I22" s="96">
         <f t="shared" si="8"/>
-        <v>58094.272499999999</v>
+        <v>0</v>
       </c>
       <c r="J22" s="146">
         <f t="shared" si="0"/>
@@ -3597,30 +3643,30 @@
       </c>
       <c r="M22" s="148">
         <f t="shared" si="2"/>
-        <v>492118.15</v>
+        <v>46728.15</v>
       </c>
       <c r="N22" s="149">
         <f t="shared" si="3"/>
-        <v>521645.15</v>
+        <v>49532.15</v>
       </c>
       <c r="O22" s="150">
         <f t="shared" si="4"/>
-        <v>506882.15</v>
+        <v>48130.15</v>
       </c>
       <c r="P22" s="51">
         <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="69">
+      <c r="B23" s="68">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="C23" s="69" t="s">
+      <c r="C23" s="68" t="s">
         <v>85</v>
       </c>
       <c r="D23" s="69"/>
@@ -3628,14 +3674,14 @@
         <v>2.6</v>
       </c>
       <c r="F23" s="78">
-        <v>-479874.84</v>
+        <v>-436483.84000000003</v>
       </c>
       <c r="G23" s="79">
         <v>0</v>
       </c>
       <c r="H23" s="80">
         <f t="shared" si="9"/>
-        <v>-479874.84</v>
+        <v>-436483.84000000003</v>
       </c>
       <c r="I23" s="80">
         <f t="shared" si="8"/>
@@ -3654,15 +3700,15 @@
       </c>
       <c r="M23" s="83">
         <f t="shared" si="2"/>
-        <v>-436483.84000000003</v>
+        <v>-393092.84</v>
       </c>
       <c r="N23" s="84">
         <f t="shared" si="3"/>
-        <v>-462672.84</v>
+        <v>-416677.84</v>
       </c>
       <c r="O23" s="85">
         <f t="shared" si="4"/>
-        <v>-449578.84</v>
+        <v>-404885.84</v>
       </c>
       <c r="P23" s="51">
         <f t="shared" si="6"/>
@@ -3670,7 +3716,7 @@
       </c>
       <c r="R23" s="50"/>
     </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="60" t="s">
         <v>16</v>
       </c>
@@ -3686,16 +3732,16 @@
         <v>4.5</v>
       </c>
       <c r="F24" s="154">
-        <v>2239721.17</v>
+        <v>2650779.17</v>
       </c>
       <c r="G24" s="154"/>
       <c r="H24" s="155">
         <f t="shared" si="9"/>
-        <v>2239721.17</v>
+        <v>2650779.17</v>
       </c>
       <c r="I24" s="155">
         <f t="shared" si="8"/>
-        <v>335958.17549999995</v>
+        <v>397616.87549999997</v>
       </c>
       <c r="J24" s="156">
         <f t="shared" si="0"/>
@@ -3710,22 +3756,22 @@
       </c>
       <c r="M24" s="158">
         <f t="shared" si="2"/>
-        <v>2650779.17</v>
+        <v>3123495.17</v>
       </c>
       <c r="N24" s="159">
         <f t="shared" si="3"/>
-        <v>2809826.17</v>
+        <v>3310905.17</v>
       </c>
       <c r="O24" s="160">
         <f t="shared" si="4"/>
-        <v>2730302.17</v>
+        <v>3217200.17</v>
       </c>
       <c r="P24" s="51">
         <f t="shared" si="6"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="60" t="s">
         <v>17</v>
       </c>
@@ -3741,19 +3787,18 @@
         <v>2.8</v>
       </c>
       <c r="F25" s="79">
-        <v>141045.18</v>
+        <v>46728.18</v>
       </c>
       <c r="G25" s="79">
-        <f>F25</f>
-        <v>141045.18</v>
+        <v>0</v>
       </c>
       <c r="H25" s="96">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>46728.18</v>
       </c>
       <c r="I25" s="96">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7009.2269999999999</v>
       </c>
       <c r="J25" s="146">
         <f t="shared" si="0"/>
@@ -3768,22 +3813,22 @@
       </c>
       <c r="M25" s="148">
         <f t="shared" si="2"/>
-        <v>46728.18</v>
+        <v>100466.18</v>
       </c>
       <c r="N25" s="149">
         <f t="shared" si="3"/>
-        <v>49532.18</v>
+        <v>106494.18</v>
       </c>
       <c r="O25" s="150">
         <f t="shared" si="4"/>
-        <v>48130.18</v>
+        <v>103480.18</v>
       </c>
       <c r="P25" s="51">
         <f t="shared" si="6"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="60" t="s">
         <v>17</v>
       </c>
@@ -3799,16 +3844,16 @@
         <v>2.8</v>
       </c>
       <c r="F26" s="79">
-        <v>661985.18999999994</v>
+        <v>808011.19</v>
       </c>
       <c r="G26" s="79"/>
       <c r="H26" s="96">
         <f t="shared" si="9"/>
-        <v>661985.18999999994</v>
+        <v>808011.19</v>
       </c>
       <c r="I26" s="96">
         <f t="shared" si="8"/>
-        <v>99297.778499999986</v>
+        <v>121201.67849999998</v>
       </c>
       <c r="J26" s="146">
         <f t="shared" si="0"/>
@@ -3823,22 +3868,22 @@
       </c>
       <c r="M26" s="148">
         <f t="shared" si="2"/>
-        <v>808011.19</v>
+        <v>975941.19</v>
       </c>
       <c r="N26" s="149">
         <f t="shared" si="3"/>
-        <v>856492.19</v>
+        <v>1034498.19</v>
       </c>
       <c r="O26" s="150">
         <f t="shared" si="4"/>
-        <v>832251.19</v>
+        <v>1005219.19</v>
       </c>
       <c r="P26" s="51">
         <f t="shared" si="6"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="60" t="s">
         <v>18</v>
       </c>
@@ -3854,18 +3899,19 @@
         <v>2.8</v>
       </c>
       <c r="F27" s="79">
-        <v>17428.2</v>
-      </c>
-      <c r="G27" s="79">
-        <v>0</v>
+        <v>66771.199999999997</v>
+      </c>
+      <c r="G27" s="217">
+        <f>F27</f>
+        <v>66771.199999999997</v>
       </c>
       <c r="H27" s="96">
         <f t="shared" si="9"/>
-        <v>17428.2</v>
+        <v>0</v>
       </c>
       <c r="I27" s="96">
         <f t="shared" si="8"/>
-        <v>2614.23</v>
+        <v>0</v>
       </c>
       <c r="J27" s="146">
         <f t="shared" si="0"/>
@@ -3880,22 +3926,22 @@
       </c>
       <c r="M27" s="148">
         <f t="shared" si="2"/>
-        <v>66771.199999999997</v>
+        <v>46728.2</v>
       </c>
       <c r="N27" s="149">
         <f t="shared" si="3"/>
-        <v>70777.2</v>
+        <v>49532.2</v>
       </c>
       <c r="O27" s="150">
         <f t="shared" si="4"/>
-        <v>68774.2</v>
+        <v>48130.2</v>
       </c>
       <c r="P27" s="51">
         <f t="shared" si="6"/>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="60" t="s">
         <v>19</v>
       </c>
@@ -3911,18 +3957,18 @@
         <v>3</v>
       </c>
       <c r="F28" s="154">
-        <v>1903233.21</v>
+        <v>2238784.21</v>
       </c>
       <c r="G28" s="154">
         <v>0</v>
       </c>
       <c r="H28" s="155">
         <f t="shared" si="9"/>
-        <v>1903233.21</v>
+        <v>2238784.21</v>
       </c>
       <c r="I28" s="155">
         <f t="shared" si="8"/>
-        <v>285484.98149999999</v>
+        <v>335817.63149999996</v>
       </c>
       <c r="J28" s="156">
         <f t="shared" si="0"/>
@@ -3937,22 +3983,22 @@
       </c>
       <c r="M28" s="158">
         <f t="shared" si="2"/>
-        <v>2238784.21</v>
+        <v>2624668.21</v>
       </c>
       <c r="N28" s="159">
         <f t="shared" si="3"/>
-        <v>2373111.21</v>
+        <v>2782148.21</v>
       </c>
       <c r="O28" s="160">
         <f t="shared" si="4"/>
-        <v>2305948.21</v>
+        <v>2703408.21</v>
       </c>
       <c r="P28" s="51">
         <f t="shared" si="6"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="60" t="s">
         <v>20</v>
       </c>
@@ -3968,18 +4014,18 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="F29" s="154">
-        <v>2601085.2200000002</v>
+        <v>3059672.22</v>
       </c>
       <c r="G29" s="154">
         <v>0</v>
       </c>
       <c r="H29" s="155">
         <f t="shared" si="9"/>
-        <v>2601085.2200000002</v>
+        <v>3059672.22</v>
       </c>
       <c r="I29" s="155">
         <f t="shared" si="8"/>
-        <v>390162.783</v>
+        <v>458950.83300000004</v>
       </c>
       <c r="J29" s="156">
         <f t="shared" si="0"/>
@@ -3994,22 +4040,22 @@
       </c>
       <c r="M29" s="158">
         <f t="shared" si="2"/>
-        <v>3059672.22</v>
+        <v>3587047.22</v>
       </c>
       <c r="N29" s="159">
         <f t="shared" si="3"/>
-        <v>3243253.22</v>
+        <v>3802270.22</v>
       </c>
       <c r="O29" s="160">
         <f t="shared" si="4"/>
-        <v>3151462.22</v>
+        <v>3694658.22</v>
       </c>
       <c r="P29" s="51">
         <f t="shared" si="6"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>21</v>
       </c>
@@ -4025,16 +4071,16 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="F30" s="78">
-        <v>1280952.23</v>
+        <v>1558208.23</v>
       </c>
       <c r="G30" s="79"/>
       <c r="H30" s="80">
         <f t="shared" si="9"/>
-        <v>1280952.23</v>
+        <v>1558208.23</v>
       </c>
       <c r="I30" s="80">
         <f t="shared" si="8"/>
-        <v>192142.8345</v>
+        <v>233731.23449999999</v>
       </c>
       <c r="J30" s="127">
         <f t="shared" si="0"/>
@@ -4049,22 +4095,22 @@
       </c>
       <c r="M30" s="83">
         <f t="shared" si="2"/>
-        <v>1558208.23</v>
+        <v>1877052.23</v>
       </c>
       <c r="N30" s="84">
         <f t="shared" si="3"/>
-        <v>1651701.23</v>
+        <v>1989675.23</v>
       </c>
       <c r="O30" s="85">
         <f t="shared" si="4"/>
-        <v>1604954.23</v>
+        <v>1933364.23</v>
       </c>
       <c r="P30" s="51">
         <f t="shared" si="6"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>24</v>
       </c>
@@ -4080,18 +4126,18 @@
         <v>5.9</v>
       </c>
       <c r="F31" s="154">
-        <v>3743024.24</v>
+        <v>4402941.24</v>
       </c>
       <c r="G31" s="154">
         <v>0</v>
       </c>
       <c r="H31" s="155">
         <f t="shared" si="9"/>
-        <v>3743024.24</v>
+        <v>4402941.24</v>
       </c>
       <c r="I31" s="155">
         <f t="shared" si="8"/>
-        <v>561453.63600000006</v>
+        <v>660441.18599999999</v>
       </c>
       <c r="J31" s="156">
         <f t="shared" si="0"/>
@@ -4106,22 +4152,22 @@
       </c>
       <c r="M31" s="158">
         <f t="shared" si="2"/>
-        <v>4402941.24</v>
+        <v>5161846.24</v>
       </c>
       <c r="N31" s="159">
         <f t="shared" si="3"/>
-        <v>4667118.24</v>
+        <v>5471557.2400000002</v>
       </c>
       <c r="O31" s="160">
         <f t="shared" si="4"/>
-        <v>4535029.24</v>
+        <v>5316701.24</v>
       </c>
       <c r="P31" s="51">
         <f t="shared" si="6"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>24</v>
       </c>
@@ -4137,7 +4183,7 @@
         <v>5.5</v>
       </c>
       <c r="F32" s="79">
-        <v>152091.25</v>
+        <v>91788.25</v>
       </c>
       <c r="G32" s="79" t="s">
         <v>76</v>
@@ -4174,7 +4220,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>24</v>
       </c>
@@ -4190,18 +4236,18 @@
         <v>6.1</v>
       </c>
       <c r="F33" s="154">
-        <v>4171076.26</v>
+        <v>4898539.26</v>
       </c>
       <c r="G33" s="154">
         <v>0</v>
       </c>
       <c r="H33" s="155">
         <f>F33-G33</f>
-        <v>4171076.26</v>
+        <v>4898539.26</v>
       </c>
       <c r="I33" s="155">
         <f t="shared" si="8"/>
-        <v>625661.4389999999</v>
+        <v>734780.88899999997</v>
       </c>
       <c r="J33" s="156">
         <f t="shared" si="0"/>
@@ -4216,15 +4262,15 @@
       </c>
       <c r="M33" s="158">
         <f t="shared" si="2"/>
-        <v>4898539.26</v>
+        <v>5735122.2599999998</v>
       </c>
       <c r="N33" s="159">
         <f t="shared" si="3"/>
-        <v>5192452.26</v>
+        <v>6079230.2599999998</v>
       </c>
       <c r="O33" s="160">
         <f t="shared" si="4"/>
-        <v>5045495.26</v>
+        <v>5907176.2599999998</v>
       </c>
       <c r="P33" s="129">
         <f t="shared" si="6"/>
@@ -4232,7 +4278,7 @@
       </c>
       <c r="Q33" s="130"/>
     </row>
-    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>24</v>
       </c>
@@ -4252,7 +4298,7 @@
       <c r="O34" s="85"/>
       <c r="P34" s="51"/>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="88"/>
       <c r="C35" s="89"/>
       <c r="D35" s="89"/>
@@ -4262,15 +4308,15 @@
       </c>
       <c r="F35" s="61">
         <f>SUM(F8:F34)</f>
-        <v>23680079.509999998</v>
+        <v>28481663.509999998</v>
       </c>
       <c r="G35" s="66">
         <f>SUM(G8:G34)</f>
-        <v>329891.28999999998</v>
+        <v>926091.54999999993</v>
       </c>
       <c r="H35" s="66">
         <f>SUM(H8:H33)</f>
-        <v>23043240.759999998</v>
+        <v>27370327.499999993</v>
       </c>
       <c r="I35" s="66"/>
       <c r="J35" s="66">
@@ -4287,113 +4333,104 @@
       </c>
       <c r="M35" s="91">
         <f t="shared" si="10"/>
-        <v>28481663.509999998</v>
+        <v>33425119.509999998</v>
       </c>
       <c r="N35" s="91">
         <f t="shared" si="10"/>
-        <v>30190567.509999998</v>
+        <v>35430631.509999998</v>
       </c>
       <c r="O35" s="91">
         <f t="shared" si="10"/>
-        <v>29145309.049999997</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>34237072.049999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="58"/>
       <c r="D36" s="58"/>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="206" t="s">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="192" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="206"/>
-      <c r="E38" s="206"/>
-      <c r="F38" s="206"/>
-      <c r="G38" s="206"/>
-      <c r="H38" s="206"/>
-      <c r="I38" s="206"/>
-      <c r="J38" s="206"/>
-      <c r="K38" s="206"/>
-      <c r="L38" s="206"/>
-      <c r="M38" s="206"/>
-    </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="206"/>
-      <c r="D39" s="206"/>
-      <c r="E39" s="206"/>
-      <c r="F39" s="206"/>
-      <c r="G39" s="206"/>
-      <c r="H39" s="206"/>
-      <c r="I39" s="206"/>
-      <c r="J39" s="206"/>
-      <c r="K39" s="206"/>
-      <c r="L39" s="206"/>
-      <c r="M39" s="206"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="206"/>
-      <c r="D40" s="206"/>
-      <c r="E40" s="206"/>
-      <c r="F40" s="206"/>
-      <c r="G40" s="206"/>
-      <c r="H40" s="206"/>
-      <c r="I40" s="206"/>
-      <c r="J40" s="206"/>
-      <c r="K40" s="206"/>
-      <c r="L40" s="206"/>
-      <c r="M40" s="206"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="206"/>
-      <c r="D41" s="206"/>
-      <c r="E41" s="206"/>
-      <c r="F41" s="206"/>
-      <c r="G41" s="206"/>
-      <c r="H41" s="206"/>
-      <c r="I41" s="206"/>
-      <c r="J41" s="206"/>
-      <c r="K41" s="206"/>
-      <c r="L41" s="206"/>
-      <c r="M41" s="206"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="206"/>
-      <c r="D42" s="206"/>
-      <c r="E42" s="206"/>
-      <c r="F42" s="206"/>
-      <c r="G42" s="206"/>
-      <c r="H42" s="206"/>
-      <c r="I42" s="206"/>
-      <c r="J42" s="206"/>
-      <c r="K42" s="206"/>
-      <c r="L42" s="206"/>
-      <c r="M42" s="206"/>
-    </row>
-    <row r="43" spans="1:17" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="206"/>
-      <c r="D43" s="206"/>
-      <c r="E43" s="206"/>
-      <c r="F43" s="206"/>
-      <c r="G43" s="206"/>
-      <c r="H43" s="206"/>
-      <c r="I43" s="206"/>
-      <c r="J43" s="206"/>
-      <c r="K43" s="206"/>
-      <c r="L43" s="206"/>
-      <c r="M43" s="206"/>
+      <c r="D38" s="192"/>
+      <c r="E38" s="192"/>
+      <c r="F38" s="192"/>
+      <c r="G38" s="192"/>
+      <c r="H38" s="192"/>
+      <c r="I38" s="192"/>
+      <c r="J38" s="192"/>
+      <c r="K38" s="192"/>
+      <c r="L38" s="192"/>
+      <c r="M38" s="192"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="192"/>
+      <c r="D39" s="192"/>
+      <c r="E39" s="192"/>
+      <c r="F39" s="192"/>
+      <c r="G39" s="192"/>
+      <c r="H39" s="192"/>
+      <c r="I39" s="192"/>
+      <c r="J39" s="192"/>
+      <c r="K39" s="192"/>
+      <c r="L39" s="192"/>
+      <c r="M39" s="192"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="192"/>
+      <c r="D40" s="192"/>
+      <c r="E40" s="192"/>
+      <c r="F40" s="192"/>
+      <c r="G40" s="192"/>
+      <c r="H40" s="192"/>
+      <c r="I40" s="192"/>
+      <c r="J40" s="192"/>
+      <c r="K40" s="192"/>
+      <c r="L40" s="192"/>
+      <c r="M40" s="192"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="192"/>
+      <c r="D41" s="192"/>
+      <c r="E41" s="192"/>
+      <c r="F41" s="192"/>
+      <c r="G41" s="192"/>
+      <c r="H41" s="192"/>
+      <c r="I41" s="192"/>
+      <c r="J41" s="192"/>
+      <c r="K41" s="192"/>
+      <c r="L41" s="192"/>
+      <c r="M41" s="192"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="192"/>
+      <c r="D42" s="192"/>
+      <c r="E42" s="192"/>
+      <c r="F42" s="192"/>
+      <c r="G42" s="192"/>
+      <c r="H42" s="192"/>
+      <c r="I42" s="192"/>
+      <c r="J42" s="192"/>
+      <c r="K42" s="192"/>
+      <c r="L42" s="192"/>
+      <c r="M42" s="192"/>
+    </row>
+    <row r="43" spans="1:17" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="192"/>
+      <c r="D43" s="192"/>
+      <c r="E43" s="192"/>
+      <c r="F43" s="192"/>
+      <c r="G43" s="192"/>
+      <c r="H43" s="192"/>
+      <c r="I43" s="192"/>
+      <c r="J43" s="192"/>
+      <c r="K43" s="192"/>
+      <c r="L43" s="192"/>
+      <c r="M43" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C38:M43"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
     <mergeCell ref="C1:F4"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
@@ -4404,6 +4441,15 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="A5:O5"/>
     <mergeCell ref="O6:O7"/>
+    <mergeCell ref="C38:M43"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4413,11 +4459,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58A25B88-8B45-4057-AF50-E99CF1B30302}">
   <dimension ref="C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C6" s="173" t="s">
-        <v>108</v>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="172" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/2026/GALERIA/Agosto/GALERIA Agosto.xlsx
+++ b/2026/GALERIA/Agosto/GALERIA Agosto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GALERIA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B2D203-C2C5-457E-9A06-EA6D0FDCEC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3035728-9EEB-460E-9DDC-B4F52E4326A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="116">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -339,9 +339,6 @@
     <t>Gastos extraordinarios a prorratear:</t>
   </si>
   <si>
-    <t xml:space="preserve">PREVISION ORDINARIA </t>
-  </si>
-  <si>
     <t xml:space="preserve">Fotocopias BYN </t>
   </si>
   <si>
@@ -372,13 +369,22 @@
     <t>Honorarios administracion - leer cartel debajo</t>
   </si>
   <si>
-    <t>A LA ADMINISTRACION SE LE DEBE EN CONCEPTO DE HONORARIOS NO COBRADOS (EN LOS MESES MENCIONADOS) UN TOTAL DEL $1.981.282,36 - LA DEUDA DESCIENDE A $1.581.282,36</t>
-  </si>
-  <si>
     <t>Deposito ya identificado 27/03</t>
   </si>
   <si>
     <t>Punitorios mal cobrados</t>
+  </si>
+  <si>
+    <t>Transf 03/08</t>
+  </si>
+  <si>
+    <t>A LA ADMINISTRACION SE LE DEBE EN CONCEPTO DE HONORARIOS NO COBRADOS (EN LOS MESES MENCIONADOS) UN TOTAL DEL $1.981.282,36 -EN JULIO SE ABONAR PARTE DE LA MISMA -  LA DEUDA DESCIENDE A $1.581.282,36 - EN AGOSTO SE VUELVE A ABONAR PARTE DE LA MISMA ($400.000) - LA DEUDA AL FINALIZAR AGOSTO SE UBICA EN: $1.181.282,36</t>
+  </si>
+  <si>
+    <t>Debito 05/08</t>
+  </si>
+  <si>
+    <t>PREVISION ORDINARIA - EDESUR</t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1013,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1241,13 +1247,13 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1302,12 +1308,48 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1338,46 +1380,9 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1830,7 +1835,7 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="17"/>
@@ -1848,7 +1853,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" s="174" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="174"/>
     </row>
@@ -1917,14 +1922,16 @@
     </row>
     <row r="22" spans="1:8" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="175" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B22" s="176"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="173">
-        <v>0</v>
-      </c>
-      <c r="E22" s="121"/>
+      <c r="D22" s="172">
+        <v>400000</v>
+      </c>
+      <c r="E22" s="121" t="s">
+        <v>112</v>
+      </c>
       <c r="F22" s="48"/>
       <c r="H22" s="22"/>
     </row>
@@ -1937,7 +1944,7 @@
       <c r="D23" s="135"/>
       <c r="E23" s="162">
         <f>D22</f>
-        <v>0</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1959,12 +1966,12 @@
         <v>149073.01</v>
       </c>
       <c r="E25" s="121" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="175" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B26" s="176"/>
       <c r="C26" s="133"/>
@@ -2010,10 +2017,12 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="169">
-        <v>0</v>
-      </c>
-      <c r="E30" s="121"/>
+      <c r="D30" s="120">
+        <v>750368</v>
+      </c>
+      <c r="E30" s="121" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
@@ -2049,7 +2058,7 @@
       <c r="D34" s="42"/>
       <c r="E34" s="99">
         <f>SUM(D29:D33)</f>
-        <v>0</v>
+        <v>750368</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2062,8 +2071,8 @@
       <c r="E35" s="102"/>
     </row>
     <row r="36" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="171" t="s">
-        <v>101</v>
+      <c r="A36" s="170" t="s">
+        <v>100</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -2096,22 +2105,24 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
       <c r="D39" s="120">
-        <v>0</v>
+        <v>34240.639999999999</v>
       </c>
       <c r="E39" s="107"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
-      <c r="D40" s="120"/>
+      <c r="D40" s="120">
+        <v>69000</v>
+      </c>
       <c r="E40" s="105"/>
     </row>
     <row r="41" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2123,7 +2134,7 @@
       <c r="D41" s="108"/>
       <c r="E41" s="99">
         <f>SUM(D39:D40)</f>
-        <v>0</v>
+        <v>103240.64</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2135,13 +2146,13 @@
     </row>
     <row r="43" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="32" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B43" s="32"/>
       <c r="C43" s="32"/>
       <c r="D43" s="110"/>
       <c r="E43" s="111">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2159,7 +2170,7 @@
       <c r="D45" s="114"/>
       <c r="E45" s="115">
         <f>(SUM(E21:E43))</f>
-        <v>1649073.01</v>
+        <v>2402681.65</v>
       </c>
       <c r="F45" s="51"/>
     </row>
@@ -2249,7 +2260,7 @@
       </c>
       <c r="B60" s="95">
         <f>E45</f>
-        <v>1649073.01</v>
+        <v>2402681.65</v>
       </c>
       <c r="D60" s="51"/>
     </row>
@@ -2259,7 +2270,7 @@
       </c>
       <c r="B61" s="95">
         <f>E45-E43</f>
-        <v>149073.01</v>
+        <v>1402681.65</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2306,7 +2317,7 @@
     <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="183" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B70" s="184"/>
       <c r="C70" s="184"/>
@@ -2320,7 +2331,7 @@
       <c r="D71" s="187"/>
       <c r="E71" s="188"/>
     </row>
-    <row r="72" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="189"/>
       <c r="B72" s="190"/>
       <c r="C72" s="190"/>
@@ -2356,7 +2367,7 @@
       </c>
       <c r="B76" s="47">
         <f>PRORRATEO!G35</f>
-        <v>926091.54999999993</v>
+        <v>1111121.19</v>
       </c>
       <c r="C76" s="23"/>
     </row>
@@ -2369,27 +2380,27 @@
     </row>
     <row r="78" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="B78" s="170">
+        <v>107</v>
+      </c>
+      <c r="B78" s="169">
         <v>-99000</v>
       </c>
       <c r="C78" s="23"/>
     </row>
     <row r="79" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="B79" s="170">
+        <v>110</v>
+      </c>
+      <c r="B79" s="169">
         <v>-270000</v>
       </c>
       <c r="C79" s="23"/>
     </row>
     <row r="80" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="B80" s="170">
+        <v>111</v>
+      </c>
+      <c r="B80" s="169">
         <v>-86980</v>
       </c>
       <c r="C80" s="23"/>
@@ -2417,9 +2428,9 @@
       <c r="A83" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="B83" s="170">
+      <c r="B83" s="169">
         <f>-B61</f>
-        <v>-149073.01</v>
+        <v>-1402681.65</v>
       </c>
       <c r="C83" s="23"/>
     </row>
@@ -2439,7 +2450,7 @@
       </c>
       <c r="B85" s="124">
         <f>SUM(B75:B84)</f>
-        <v>1553039.93</v>
+        <v>484460.93000000017</v>
       </c>
       <c r="C85" s="26"/>
       <c r="D85" s="151"/>
@@ -2625,12 +2636,12 @@
     <row r="1" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
-      <c r="C1" s="205" t="s">
+      <c r="C1" s="192" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -2645,10 +2656,10 @@
     <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="206"/>
-      <c r="D2" s="206"/>
-      <c r="E2" s="206"/>
-      <c r="F2" s="206"/>
+      <c r="C2" s="193"/>
+      <c r="D2" s="193"/>
+      <c r="E2" s="193"/>
+      <c r="F2" s="193"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -2663,10 +2674,10 @@
     <row r="3" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
-      <c r="C3" s="206"/>
-      <c r="D3" s="206"/>
-      <c r="E3" s="206"/>
-      <c r="F3" s="206"/>
+      <c r="C3" s="193"/>
+      <c r="D3" s="193"/>
+      <c r="E3" s="193"/>
+      <c r="F3" s="193"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -2674,25 +2685,25 @@
         <v>80</v>
       </c>
       <c r="K3" s="6"/>
-      <c r="L3" s="207">
+      <c r="L3" s="194">
         <f>Q3</f>
-        <v>1668874.9300000002</v>
-      </c>
-      <c r="M3" s="207"/>
+        <v>2402681.65</v>
+      </c>
+      <c r="M3" s="194"/>
       <c r="N3" s="62"/>
       <c r="O3" s="62"/>
       <c r="P3" s="22"/>
       <c r="Q3">
-        <v>1668874.9300000002</v>
+        <v>2402681.65</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="206"/>
-      <c r="D4" s="206"/>
-      <c r="E4" s="206"/>
-      <c r="F4" s="206"/>
+      <c r="C4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -2700,97 +2711,97 @@
         <v>99</v>
       </c>
       <c r="K4" s="6"/>
-      <c r="L4" s="208"/>
-      <c r="M4" s="208"/>
+      <c r="L4" s="195"/>
+      <c r="M4" s="195"/>
       <c r="N4" s="64"/>
       <c r="O4" s="64"/>
     </row>
     <row r="5" spans="1:18" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="211" t="s">
+      <c r="A5" s="200" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="212"/>
-      <c r="C5" s="212"/>
-      <c r="D5" s="212"/>
-      <c r="E5" s="212"/>
-      <c r="F5" s="212"/>
-      <c r="G5" s="212"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="212"/>
-      <c r="K5" s="212"/>
-      <c r="L5" s="212"/>
-      <c r="M5" s="212"/>
-      <c r="N5" s="212"/>
-      <c r="O5" s="213"/>
+      <c r="B5" s="201"/>
+      <c r="C5" s="201"/>
+      <c r="D5" s="201"/>
+      <c r="E5" s="201"/>
+      <c r="F5" s="201"/>
+      <c r="G5" s="201"/>
+      <c r="H5" s="201"/>
+      <c r="I5" s="201"/>
+      <c r="J5" s="201"/>
+      <c r="K5" s="201"/>
+      <c r="L5" s="201"/>
+      <c r="M5" s="201"/>
+      <c r="N5" s="201"/>
+      <c r="O5" s="202"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="209" t="s">
+      <c r="A6" s="196" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="193" t="s">
+      <c r="B6" s="198" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="193" t="s">
+      <c r="C6" s="198" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="193" t="s">
+      <c r="D6" s="198" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="193" t="s">
+      <c r="E6" s="198" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="193" t="s">
+      <c r="F6" s="198" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="193" t="s">
+      <c r="G6" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="202" t="s">
+      <c r="H6" s="214" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="202" t="s">
+      <c r="I6" s="214" t="s">
         <v>87</v>
       </c>
-      <c r="J6" s="197" t="s">
+      <c r="J6" s="209" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="197" t="s">
+      <c r="K6" s="209" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="200" t="s">
+      <c r="L6" s="212" t="s">
         <v>54</v>
       </c>
       <c r="M6" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="195" t="s">
+      <c r="N6" s="207" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="214" t="s">
+      <c r="O6" s="203" t="s">
         <v>52</v>
       </c>
       <c r="R6" s="51"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="210"/>
-      <c r="B7" s="204"/>
-      <c r="C7" s="204"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="204"/>
-      <c r="F7" s="204"/>
-      <c r="G7" s="204"/>
-      <c r="H7" s="203"/>
-      <c r="I7" s="203"/>
-      <c r="J7" s="198"/>
-      <c r="K7" s="199"/>
-      <c r="L7" s="201"/>
+      <c r="A7" s="197"/>
+      <c r="B7" s="199"/>
+      <c r="C7" s="199"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="199"/>
+      <c r="F7" s="199"/>
+      <c r="G7" s="199"/>
+      <c r="H7" s="215"/>
+      <c r="I7" s="215"/>
+      <c r="J7" s="210"/>
+      <c r="K7" s="211"/>
+      <c r="L7" s="213"/>
       <c r="M7" s="65" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="N7" s="196"/>
-      <c r="O7" s="215"/>
+      <c r="N7" s="208"/>
+      <c r="O7" s="204"/>
     </row>
     <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
@@ -2826,22 +2837,22 @@
       </c>
       <c r="K8" s="127">
         <f t="shared" ref="K8:K33" si="1">L$3*E8/100</f>
-        <v>113483.49524</v>
+        <v>163382.35219999999</v>
       </c>
       <c r="L8" s="82">
         <v>0</v>
       </c>
       <c r="M8" s="83">
         <f t="shared" ref="M8:M33" si="2">ROUND(SUM(H8:L8),0) + P8</f>
-        <v>696997.01</v>
+        <v>746896.01</v>
       </c>
       <c r="N8" s="84">
         <f>ROUND(M8*6% + M8,0) + P8</f>
-        <v>738817.01</v>
+        <v>791710.01</v>
       </c>
       <c r="O8" s="85">
         <f>ROUND(M8*3%,0) + M8</f>
-        <v>717907.01</v>
+        <v>769303.01</v>
       </c>
       <c r="P8" s="51">
         <v>0.01</v>
@@ -2882,22 +2893,22 @@
       </c>
       <c r="K9" s="146">
         <f t="shared" si="1"/>
-        <v>85112.621430000014</v>
+        <v>122536.76414999999</v>
       </c>
       <c r="L9" s="147">
         <v>0</v>
       </c>
       <c r="M9" s="148">
         <f t="shared" si="2"/>
-        <v>-197220.98</v>
+        <v>-159796.98000000001</v>
       </c>
       <c r="N9" s="149">
         <f t="shared" ref="N9:N33" si="3">ROUND(M9*6% + M9,0) + P9</f>
-        <v>-209053.98</v>
+        <v>-169384.98</v>
       </c>
       <c r="O9" s="150">
         <f t="shared" ref="O9:O33" si="4">ROUND(M9*3%,0) + M9</f>
-        <v>-203137.98</v>
+        <v>-164590.98000000001</v>
       </c>
       <c r="P9" s="51">
         <f>P8+0.01</f>
@@ -2926,7 +2937,7 @@
       <c r="F10" s="79">
         <v>93457.03</v>
       </c>
-      <c r="G10" s="217">
+      <c r="G10" s="173">
         <f>F10</f>
         <v>93457.03</v>
       </c>
@@ -2944,22 +2955,22 @@
       </c>
       <c r="K10" s="146">
         <f t="shared" si="1"/>
-        <v>93456.996080000012</v>
+        <v>134550.17239999998</v>
       </c>
       <c r="L10" s="147">
         <v>0</v>
       </c>
       <c r="M10" s="148">
         <f t="shared" si="2"/>
-        <v>93457.03</v>
+        <v>134550.03</v>
       </c>
       <c r="N10" s="149">
         <f t="shared" si="3"/>
-        <v>99064.03</v>
+        <v>142623.03</v>
       </c>
       <c r="O10" s="150">
         <f t="shared" si="4"/>
-        <v>96261.03</v>
+        <v>138587.03</v>
       </c>
       <c r="P10" s="51">
         <f t="shared" ref="P10:P33" si="6">P9+0.01</f>
@@ -3001,22 +3012,22 @@
       </c>
       <c r="K11" s="127">
         <f t="shared" si="1"/>
-        <v>46728.498040000006</v>
+        <v>67275.086199999991</v>
       </c>
       <c r="L11" s="82">
         <v>0</v>
       </c>
       <c r="M11" s="83">
         <f t="shared" si="2"/>
-        <v>-1072062.96</v>
+        <v>-1051516.96</v>
       </c>
       <c r="N11" s="84">
         <f t="shared" si="3"/>
-        <v>-1136386.96</v>
+        <v>-1114607.96</v>
       </c>
       <c r="O11" s="85">
         <f t="shared" si="4"/>
-        <v>-1104224.96</v>
+        <v>-1083062.96</v>
       </c>
       <c r="P11" s="51">
         <f t="shared" si="6"/>
@@ -3044,7 +3055,7 @@
       <c r="F12" s="78">
         <v>133955.04999999999</v>
       </c>
-      <c r="G12" s="217">
+      <c r="G12" s="173">
         <f>137974.05</f>
         <v>137974.04999999999</v>
       </c>
@@ -3062,22 +3073,22 @@
       </c>
       <c r="K12" s="127">
         <f t="shared" si="1"/>
-        <v>46728.498040000006</v>
+        <v>67275.086199999991</v>
       </c>
       <c r="L12" s="82">
         <v>0</v>
       </c>
       <c r="M12" s="83">
         <f t="shared" si="2"/>
-        <v>42709.05</v>
+        <v>63256.05</v>
       </c>
       <c r="N12" s="84">
         <f t="shared" si="3"/>
-        <v>45272.05</v>
+        <v>67051.05</v>
       </c>
       <c r="O12" s="85">
         <f t="shared" si="4"/>
-        <v>43990.05</v>
+        <v>65154.05</v>
       </c>
       <c r="P12" s="51">
         <f t="shared" si="6"/>
@@ -3120,22 +3131,22 @@
       </c>
       <c r="K13" s="127">
         <f t="shared" si="1"/>
-        <v>46728.498040000006</v>
+        <v>67275.086199999991</v>
       </c>
       <c r="L13" s="82">
         <v>0</v>
       </c>
       <c r="M13" s="83">
         <f t="shared" si="2"/>
-        <v>19245.060000000001</v>
+        <v>39791.06</v>
       </c>
       <c r="N13" s="84">
         <f t="shared" si="3"/>
-        <v>20400.060000000001</v>
+        <v>42179.06</v>
       </c>
       <c r="O13" s="85">
         <f t="shared" si="4"/>
-        <v>19822.060000000001</v>
+        <v>40985.06</v>
       </c>
       <c r="P13" s="51">
         <f t="shared" si="6"/>
@@ -3180,22 +3191,22 @@
       </c>
       <c r="K14" s="156">
         <f t="shared" si="1"/>
-        <v>66754.997200000013</v>
+        <v>96107.266000000003</v>
       </c>
       <c r="L14" s="157">
         <v>0</v>
       </c>
       <c r="M14" s="158">
         <f t="shared" si="2"/>
-        <v>3499557.07</v>
+        <v>3528909.07</v>
       </c>
       <c r="N14" s="159">
         <f t="shared" si="3"/>
-        <v>3709530.07</v>
+        <v>3740644.07</v>
       </c>
       <c r="O14" s="160">
         <f t="shared" si="4"/>
-        <v>3604544.07</v>
+        <v>3634776.07</v>
       </c>
       <c r="P14" s="51">
         <f t="shared" si="6"/>
@@ -3237,22 +3248,22 @@
       </c>
       <c r="K15" s="140">
         <f t="shared" si="1"/>
-        <v>53403.997760000006</v>
+        <v>76885.8128</v>
       </c>
       <c r="L15" s="141">
         <v>0</v>
       </c>
       <c r="M15" s="142">
         <f t="shared" si="2"/>
-        <v>114819.08</v>
+        <v>138301.07999999999</v>
       </c>
       <c r="N15" s="143">
         <f t="shared" si="3"/>
-        <v>121708.08</v>
+        <v>146599.07999999999</v>
       </c>
       <c r="O15" s="144">
         <f t="shared" si="4"/>
-        <v>118264.08</v>
+        <v>142450.07999999999</v>
       </c>
       <c r="P15" s="51">
         <f t="shared" si="6"/>
@@ -3294,22 +3305,22 @@
       </c>
       <c r="K16" s="156">
         <f t="shared" si="1"/>
-        <v>46728.498040000006</v>
+        <v>67275.086199999991</v>
       </c>
       <c r="L16" s="157">
         <v>0</v>
       </c>
       <c r="M16" s="158">
         <f t="shared" si="2"/>
-        <v>3037660.09</v>
+        <v>3058207.09</v>
       </c>
       <c r="N16" s="159">
         <f t="shared" si="3"/>
-        <v>3219920.09</v>
+        <v>3241700.09</v>
       </c>
       <c r="O16" s="160">
         <f t="shared" si="4"/>
-        <v>3128790.09</v>
+        <v>3149953.09</v>
       </c>
       <c r="P16" s="51">
         <f t="shared" si="6"/>
@@ -3348,18 +3359,18 @@
       </c>
       <c r="K17" s="127">
         <f t="shared" si="1"/>
-        <v>46728.498040000006</v>
+        <v>67275.086199999991</v>
       </c>
       <c r="L17" s="82">
         <v>0</v>
       </c>
       <c r="M17" s="83">
         <f t="shared" si="2"/>
-        <v>46728.1</v>
+        <v>67275.100000000006</v>
       </c>
       <c r="N17" s="84">
         <f t="shared" si="3"/>
-        <v>49532.1</v>
+        <v>71312.100000000006</v>
       </c>
       <c r="O17" s="79" t="s">
         <v>76</v>
@@ -3401,18 +3412,18 @@
       </c>
       <c r="K18" s="127">
         <f t="shared" si="1"/>
-        <v>46728.498040000006</v>
+        <v>67275.086199999991</v>
       </c>
       <c r="L18" s="82">
         <v>0</v>
       </c>
       <c r="M18" s="83">
         <f t="shared" si="2"/>
-        <v>46728.11</v>
+        <v>67275.11</v>
       </c>
       <c r="N18" s="84">
         <f t="shared" si="3"/>
-        <v>49532.11</v>
+        <v>71312.11</v>
       </c>
       <c r="O18" s="79" t="s">
         <v>76</v>
@@ -3440,7 +3451,7 @@
       <c r="F19" s="79">
         <v>135771.12</v>
       </c>
-      <c r="G19" s="217">
+      <c r="G19" s="173">
         <f>F19</f>
         <v>135771.12</v>
       </c>
@@ -3458,22 +3469,22 @@
       </c>
       <c r="K19" s="146">
         <f t="shared" si="1"/>
-        <v>46728.498040000006</v>
+        <v>67275.086199999991</v>
       </c>
       <c r="L19" s="147">
         <v>0</v>
       </c>
       <c r="M19" s="148">
         <f t="shared" si="2"/>
-        <v>46728.12</v>
+        <v>67275.12</v>
       </c>
       <c r="N19" s="149">
         <f t="shared" si="3"/>
-        <v>49532.12</v>
+        <v>71312.12</v>
       </c>
       <c r="O19" s="150">
         <f t="shared" si="4"/>
-        <v>48130.12</v>
+        <v>69293.119999999995</v>
       </c>
       <c r="P19" s="51">
         <f t="shared" si="6"/>
@@ -3498,16 +3509,16 @@
       <c r="F20" s="79">
         <v>1666904.13</v>
       </c>
-      <c r="G20" s="79">
-        <v>0</v>
+      <c r="G20" s="173">
+        <v>141029.64000000001</v>
       </c>
       <c r="H20" s="96">
         <f t="shared" si="9"/>
-        <v>1666904.13</v>
+        <v>1525874.4899999998</v>
       </c>
       <c r="I20" s="96">
         <f t="shared" si="8"/>
-        <v>250035.61949999997</v>
+        <v>228881.17349999995</v>
       </c>
       <c r="J20" s="146">
         <f t="shared" si="0"/>
@@ -3515,22 +3526,22 @@
       </c>
       <c r="K20" s="146">
         <f t="shared" si="1"/>
-        <v>85112.621430000014</v>
+        <v>122536.76414999999</v>
       </c>
       <c r="L20" s="147">
         <v>0</v>
       </c>
       <c r="M20" s="148">
         <f t="shared" si="2"/>
-        <v>2002052.13</v>
+        <v>1877292.13</v>
       </c>
       <c r="N20" s="149">
         <f t="shared" si="3"/>
-        <v>2122175.13</v>
+        <v>1989930.13</v>
       </c>
       <c r="O20" s="150">
         <f t="shared" si="4"/>
-        <v>2062114.13</v>
+        <v>1933611.13</v>
       </c>
       <c r="P20" s="51">
         <f t="shared" si="6"/>
@@ -3575,22 +3586,22 @@
       </c>
       <c r="K21" s="156">
         <f t="shared" si="1"/>
-        <v>43390.74818000001</v>
+        <v>62469.722900000001</v>
       </c>
       <c r="L21" s="157">
         <v>0</v>
       </c>
       <c r="M21" s="158">
         <f t="shared" si="2"/>
-        <v>2069932.14</v>
+        <v>2089011.14</v>
       </c>
       <c r="N21" s="159">
         <f t="shared" si="3"/>
-        <v>2194128.14</v>
+        <v>2214352.14</v>
       </c>
       <c r="O21" s="160">
         <f t="shared" si="4"/>
-        <v>2132030.1399999997</v>
+        <v>2151681.1399999997</v>
       </c>
       <c r="P21" s="51">
         <f t="shared" si="6"/>
@@ -3618,7 +3629,7 @@
       <c r="F22" s="79">
         <v>492118.15</v>
       </c>
-      <c r="G22" s="217">
+      <c r="G22" s="173">
         <f>135138.15+270000+86980</f>
         <v>492118.15</v>
       </c>
@@ -3636,22 +3647,22 @@
       </c>
       <c r="K22" s="146">
         <f t="shared" si="1"/>
-        <v>46728.498040000006</v>
+        <v>67275.086199999991</v>
       </c>
       <c r="L22" s="147">
         <v>0</v>
       </c>
       <c r="M22" s="148">
         <f t="shared" si="2"/>
-        <v>46728.15</v>
+        <v>67275.149999999994</v>
       </c>
       <c r="N22" s="149">
         <f t="shared" si="3"/>
-        <v>49532.15</v>
+        <v>71312.149999999994</v>
       </c>
       <c r="O22" s="150">
         <f t="shared" si="4"/>
-        <v>48130.15</v>
+        <v>69293.149999999994</v>
       </c>
       <c r="P22" s="51">
         <f t="shared" si="6"/>
@@ -3676,12 +3687,12 @@
       <c r="F23" s="78">
         <v>-436483.84000000003</v>
       </c>
-      <c r="G23" s="79">
-        <v>0</v>
+      <c r="G23" s="173">
+        <v>44000</v>
       </c>
       <c r="H23" s="80">
         <f t="shared" si="9"/>
-        <v>-436483.84000000003</v>
+        <v>-480483.84000000003</v>
       </c>
       <c r="I23" s="80">
         <f t="shared" si="8"/>
@@ -3693,22 +3704,22 @@
       </c>
       <c r="K23" s="127">
         <f t="shared" si="1"/>
-        <v>43390.74818000001</v>
+        <v>62469.722900000001</v>
       </c>
       <c r="L23" s="82">
         <v>0</v>
       </c>
       <c r="M23" s="83">
         <f t="shared" si="2"/>
-        <v>-393092.84</v>
+        <v>-418013.84</v>
       </c>
       <c r="N23" s="84">
         <f t="shared" si="3"/>
-        <v>-416677.84</v>
+        <v>-443094.84</v>
       </c>
       <c r="O23" s="85">
         <f t="shared" si="4"/>
-        <v>-404885.84</v>
+        <v>-430553.84</v>
       </c>
       <c r="P23" s="51">
         <f t="shared" si="6"/>
@@ -3749,22 +3760,22 @@
       </c>
       <c r="K24" s="156">
         <f t="shared" si="1"/>
-        <v>75099.37185000001</v>
+        <v>108120.67424999998</v>
       </c>
       <c r="L24" s="157">
         <v>0</v>
       </c>
       <c r="M24" s="158">
         <f t="shared" si="2"/>
-        <v>3123495.17</v>
+        <v>3156517.17</v>
       </c>
       <c r="N24" s="159">
         <f t="shared" si="3"/>
-        <v>3310905.17</v>
+        <v>3345908.17</v>
       </c>
       <c r="O24" s="160">
         <f t="shared" si="4"/>
-        <v>3217200.17</v>
+        <v>3251213.17</v>
       </c>
       <c r="P24" s="51">
         <f t="shared" si="6"/>
@@ -3806,22 +3817,22 @@
       </c>
       <c r="K25" s="146">
         <f t="shared" si="1"/>
-        <v>46728.498040000006</v>
+        <v>67275.086199999991</v>
       </c>
       <c r="L25" s="147">
         <v>0</v>
       </c>
       <c r="M25" s="148">
         <f t="shared" si="2"/>
-        <v>100466.18</v>
+        <v>121012.18</v>
       </c>
       <c r="N25" s="149">
         <f t="shared" si="3"/>
-        <v>106494.18</v>
+        <v>128273.18</v>
       </c>
       <c r="O25" s="150">
         <f t="shared" si="4"/>
-        <v>103480.18</v>
+        <v>124642.18</v>
       </c>
       <c r="P25" s="51">
         <f t="shared" si="6"/>
@@ -3861,22 +3872,22 @@
       </c>
       <c r="K26" s="146">
         <f t="shared" si="1"/>
-        <v>46728.498040000006</v>
+        <v>67275.086199999991</v>
       </c>
       <c r="L26" s="147">
         <v>0</v>
       </c>
       <c r="M26" s="148">
         <f t="shared" si="2"/>
-        <v>975941.19</v>
+        <v>996488.19</v>
       </c>
       <c r="N26" s="149">
         <f t="shared" si="3"/>
-        <v>1034498.19</v>
+        <v>1056277.19</v>
       </c>
       <c r="O26" s="150">
         <f t="shared" si="4"/>
-        <v>1005219.19</v>
+        <v>1026383.19</v>
       </c>
       <c r="P26" s="51">
         <f t="shared" si="6"/>
@@ -3901,7 +3912,7 @@
       <c r="F27" s="79">
         <v>66771.199999999997</v>
       </c>
-      <c r="G27" s="217">
+      <c r="G27" s="173">
         <f>F27</f>
         <v>66771.199999999997</v>
       </c>
@@ -3919,22 +3930,22 @@
       </c>
       <c r="K27" s="146">
         <f t="shared" si="1"/>
-        <v>46728.498040000006</v>
+        <v>67275.086199999991</v>
       </c>
       <c r="L27" s="147">
         <v>0</v>
       </c>
       <c r="M27" s="148">
         <f t="shared" si="2"/>
-        <v>46728.2</v>
+        <v>67275.199999999997</v>
       </c>
       <c r="N27" s="149">
         <f t="shared" si="3"/>
-        <v>49532.2</v>
+        <v>71312.2</v>
       </c>
       <c r="O27" s="150">
         <f t="shared" si="4"/>
-        <v>48130.2</v>
+        <v>69293.2</v>
       </c>
       <c r="P27" s="51">
         <f t="shared" si="6"/>
@@ -3976,22 +3987,22 @@
       </c>
       <c r="K28" s="156">
         <f t="shared" si="1"/>
-        <v>50066.247900000009</v>
+        <v>72080.449499999988</v>
       </c>
       <c r="L28" s="157">
         <v>0</v>
       </c>
       <c r="M28" s="158">
         <f t="shared" si="2"/>
-        <v>2624668.21</v>
+        <v>2646682.21</v>
       </c>
       <c r="N28" s="159">
         <f t="shared" si="3"/>
-        <v>2782148.21</v>
+        <v>2805483.21</v>
       </c>
       <c r="O28" s="160">
         <f t="shared" si="4"/>
-        <v>2703408.21</v>
+        <v>2726082.21</v>
       </c>
       <c r="P28" s="51">
         <f t="shared" si="6"/>
@@ -4033,22 +4044,22 @@
       </c>
       <c r="K29" s="156">
         <f t="shared" si="1"/>
-        <v>68423.872130000003</v>
+        <v>98509.947649999987</v>
       </c>
       <c r="L29" s="157">
         <v>0</v>
       </c>
       <c r="M29" s="158">
         <f t="shared" si="2"/>
-        <v>3587047.22</v>
+        <v>3617133.22</v>
       </c>
       <c r="N29" s="159">
         <f t="shared" si="3"/>
-        <v>3802270.22</v>
+        <v>3834161.22</v>
       </c>
       <c r="O29" s="160">
         <f t="shared" si="4"/>
-        <v>3694658.22</v>
+        <v>3725647.22</v>
       </c>
       <c r="P29" s="51">
         <f t="shared" si="6"/>
@@ -4088,22 +4099,22 @@
       </c>
       <c r="K30" s="127">
         <f t="shared" si="1"/>
-        <v>85112.621430000014</v>
+        <v>122536.76414999999</v>
       </c>
       <c r="L30" s="82">
         <v>0</v>
       </c>
       <c r="M30" s="83">
         <f t="shared" si="2"/>
-        <v>1877052.23</v>
+        <v>1914476.23</v>
       </c>
       <c r="N30" s="84">
         <f t="shared" si="3"/>
-        <v>1989675.23</v>
+        <v>2029345.23</v>
       </c>
       <c r="O30" s="85">
         <f t="shared" si="4"/>
-        <v>1933364.23</v>
+        <v>1971910.23</v>
       </c>
       <c r="P30" s="51">
         <f t="shared" si="6"/>
@@ -4145,22 +4156,22 @@
       </c>
       <c r="K31" s="156">
         <f t="shared" si="1"/>
-        <v>98463.620870000013</v>
+        <v>141758.21734999999</v>
       </c>
       <c r="L31" s="157">
         <v>0</v>
       </c>
       <c r="M31" s="158">
         <f t="shared" si="2"/>
-        <v>5161846.24</v>
+        <v>5205141.24</v>
       </c>
       <c r="N31" s="159">
         <f t="shared" si="3"/>
-        <v>5471557.2400000002</v>
+        <v>5517450.2400000002</v>
       </c>
       <c r="O31" s="160">
         <f t="shared" si="4"/>
-        <v>5316701.24</v>
+        <v>5361295.24</v>
       </c>
       <c r="P31" s="51">
         <f t="shared" si="6"/>
@@ -4199,18 +4210,18 @@
       </c>
       <c r="K32" s="127">
         <f t="shared" si="1"/>
-        <v>91788.121150000006</v>
+        <v>132147.49075</v>
       </c>
       <c r="L32" s="82">
         <v>0</v>
       </c>
       <c r="M32" s="131">
         <f t="shared" si="2"/>
-        <v>91788.25</v>
+        <v>132147.25</v>
       </c>
       <c r="N32" s="132">
         <f t="shared" si="3"/>
-        <v>97296.25</v>
+        <v>140076.25</v>
       </c>
       <c r="O32" s="79" t="s">
         <v>76</v>
@@ -4255,22 +4266,22 @@
       </c>
       <c r="K33" s="156">
         <f t="shared" si="1"/>
-        <v>101801.37073000001</v>
+        <v>146563.58064999999</v>
       </c>
       <c r="L33" s="157">
         <v>0</v>
       </c>
       <c r="M33" s="158">
         <f t="shared" si="2"/>
-        <v>5735122.2599999998</v>
+        <v>5779884.2599999998</v>
       </c>
       <c r="N33" s="159">
         <f t="shared" si="3"/>
-        <v>6079230.2599999998</v>
+        <v>6126677.2599999998</v>
       </c>
       <c r="O33" s="160">
         <f t="shared" si="4"/>
-        <v>5907176.2599999998</v>
+        <v>5953281.2599999998</v>
       </c>
       <c r="P33" s="129">
         <f t="shared" si="6"/>
@@ -4312,11 +4323,11 @@
       </c>
       <c r="G35" s="66">
         <f>SUM(G8:G34)</f>
-        <v>926091.54999999993</v>
+        <v>1111121.19</v>
       </c>
       <c r="H35" s="66">
         <f>SUM(H8:H33)</f>
-        <v>27370327.499999993</v>
+        <v>27185297.859999992</v>
       </c>
       <c r="I35" s="66"/>
       <c r="J35" s="66">
@@ -4325,7 +4336,7 @@
       </c>
       <c r="K35" s="61">
         <f t="shared" si="10"/>
-        <v>1668874.9300000002</v>
+        <v>2402681.6499999994</v>
       </c>
       <c r="L35" s="66">
         <f t="shared" si="10"/>
@@ -4333,15 +4344,15 @@
       </c>
       <c r="M35" s="91">
         <f t="shared" si="10"/>
-        <v>33425119.509999998</v>
+        <v>33952743.509999998</v>
       </c>
       <c r="N35" s="91">
         <f t="shared" si="10"/>
-        <v>35430631.509999998</v>
+        <v>35989913.509999998</v>
       </c>
       <c r="O35" s="91">
         <f t="shared" si="10"/>
-        <v>34237072.049999997</v>
+        <v>34696627.049999997</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4350,87 +4361,96 @@
     </row>
     <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="192" t="s">
+      <c r="C38" s="205" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="192"/>
-      <c r="E38" s="192"/>
-      <c r="F38" s="192"/>
-      <c r="G38" s="192"/>
-      <c r="H38" s="192"/>
-      <c r="I38" s="192"/>
-      <c r="J38" s="192"/>
-      <c r="K38" s="192"/>
-      <c r="L38" s="192"/>
-      <c r="M38" s="192"/>
+      <c r="D38" s="205"/>
+      <c r="E38" s="205"/>
+      <c r="F38" s="205"/>
+      <c r="G38" s="205"/>
+      <c r="H38" s="205"/>
+      <c r="I38" s="205"/>
+      <c r="J38" s="205"/>
+      <c r="K38" s="205"/>
+      <c r="L38" s="205"/>
+      <c r="M38" s="205"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="192"/>
-      <c r="D39" s="192"/>
-      <c r="E39" s="192"/>
-      <c r="F39" s="192"/>
-      <c r="G39" s="192"/>
-      <c r="H39" s="192"/>
-      <c r="I39" s="192"/>
-      <c r="J39" s="192"/>
-      <c r="K39" s="192"/>
-      <c r="L39" s="192"/>
-      <c r="M39" s="192"/>
+      <c r="C39" s="205"/>
+      <c r="D39" s="205"/>
+      <c r="E39" s="205"/>
+      <c r="F39" s="205"/>
+      <c r="G39" s="205"/>
+      <c r="H39" s="205"/>
+      <c r="I39" s="205"/>
+      <c r="J39" s="205"/>
+      <c r="K39" s="205"/>
+      <c r="L39" s="205"/>
+      <c r="M39" s="205"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="192"/>
-      <c r="D40" s="192"/>
-      <c r="E40" s="192"/>
-      <c r="F40" s="192"/>
-      <c r="G40" s="192"/>
-      <c r="H40" s="192"/>
-      <c r="I40" s="192"/>
-      <c r="J40" s="192"/>
-      <c r="K40" s="192"/>
-      <c r="L40" s="192"/>
-      <c r="M40" s="192"/>
+      <c r="C40" s="205"/>
+      <c r="D40" s="205"/>
+      <c r="E40" s="205"/>
+      <c r="F40" s="205"/>
+      <c r="G40" s="205"/>
+      <c r="H40" s="205"/>
+      <c r="I40" s="205"/>
+      <c r="J40" s="205"/>
+      <c r="K40" s="205"/>
+      <c r="L40" s="205"/>
+      <c r="M40" s="205"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="192"/>
-      <c r="D41" s="192"/>
-      <c r="E41" s="192"/>
-      <c r="F41" s="192"/>
-      <c r="G41" s="192"/>
-      <c r="H41" s="192"/>
-      <c r="I41" s="192"/>
-      <c r="J41" s="192"/>
-      <c r="K41" s="192"/>
-      <c r="L41" s="192"/>
-      <c r="M41" s="192"/>
+      <c r="C41" s="205"/>
+      <c r="D41" s="205"/>
+      <c r="E41" s="205"/>
+      <c r="F41" s="205"/>
+      <c r="G41" s="205"/>
+      <c r="H41" s="205"/>
+      <c r="I41" s="205"/>
+      <c r="J41" s="205"/>
+      <c r="K41" s="205"/>
+      <c r="L41" s="205"/>
+      <c r="M41" s="205"/>
     </row>
     <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="192"/>
-      <c r="D42" s="192"/>
-      <c r="E42" s="192"/>
-      <c r="F42" s="192"/>
-      <c r="G42" s="192"/>
-      <c r="H42" s="192"/>
-      <c r="I42" s="192"/>
-      <c r="J42" s="192"/>
-      <c r="K42" s="192"/>
-      <c r="L42" s="192"/>
-      <c r="M42" s="192"/>
+      <c r="C42" s="205"/>
+      <c r="D42" s="205"/>
+      <c r="E42" s="205"/>
+      <c r="F42" s="205"/>
+      <c r="G42" s="205"/>
+      <c r="H42" s="205"/>
+      <c r="I42" s="205"/>
+      <c r="J42" s="205"/>
+      <c r="K42" s="205"/>
+      <c r="L42" s="205"/>
+      <c r="M42" s="205"/>
     </row>
     <row r="43" spans="1:17" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="192"/>
-      <c r="D43" s="192"/>
-      <c r="E43" s="192"/>
-      <c r="F43" s="192"/>
-      <c r="G43" s="192"/>
-      <c r="H43" s="192"/>
-      <c r="I43" s="192"/>
-      <c r="J43" s="192"/>
-      <c r="K43" s="192"/>
-      <c r="L43" s="192"/>
-      <c r="M43" s="192"/>
+      <c r="C43" s="205"/>
+      <c r="D43" s="205"/>
+      <c r="E43" s="205"/>
+      <c r="F43" s="205"/>
+      <c r="G43" s="205"/>
+      <c r="H43" s="205"/>
+      <c r="I43" s="205"/>
+      <c r="J43" s="205"/>
+      <c r="K43" s="205"/>
+      <c r="L43" s="205"/>
+      <c r="M43" s="205"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C38:M43"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
     <mergeCell ref="C1:F4"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
@@ -4441,15 +4461,6 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="A5:O5"/>
     <mergeCell ref="O6:O7"/>
-    <mergeCell ref="C38:M43"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4462,8 +4473,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="6" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C6" s="172" t="s">
-        <v>104</v>
+      <c r="C6" s="171" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
